--- a/Versão5/PRO/Ontologia_Genetica.xlsx
+++ b/Versão5/PRO/Ontologia_Genetica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E5EDCF-A8A7-4217-9C25-70535EB12308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DE17C2-D888-4071-905A-D7666D59D5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="237">
   <si>
     <t>Key</t>
   </si>
@@ -1555,9 +1555,6 @@
     <t>CategoriaRvt</t>
   </si>
   <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -1606,9 +1603,6 @@
     <t>Formalizar conceptos de las  Estructuras Genéticamente Construídas</t>
   </si>
   <si>
-    <t>Movimento.Geométrico</t>
-  </si>
-  <si>
     <t>Giro</t>
   </si>
   <si>
@@ -1618,9 +1612,6 @@
     <t>Reflexão</t>
   </si>
   <si>
-    <t>Parâmetro.Geométrico</t>
-  </si>
-  <si>
     <t>Ponto.Base</t>
   </si>
   <si>
@@ -1732,12 +1723,6 @@
     <t>Reflexão. Transformação de uma ponto em relação a um eixo de simetria. Precisa Ponto Eixo1 e Ponto Eixo2.</t>
   </si>
   <si>
-    <t>Bases.Geométricas</t>
-  </si>
-  <si>
-    <t>Elementos.TGB</t>
-  </si>
-  <si>
     <t>Punto final de un vector de traslación</t>
   </si>
   <si>
@@ -1919,6 +1904,75 @@
   </si>
   <si>
     <t>Formantes</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Morfológico</t>
+  </si>
+  <si>
+    <t>Código.De.Forma</t>
+  </si>
+  <si>
+    <t>Códificação.Formal</t>
+  </si>
+  <si>
+    <t>Morfologias</t>
+  </si>
+  <si>
+    <t>Código formal do projeto de acordo à técnica EGC</t>
+  </si>
+  <si>
+    <t>Elementos.EGC</t>
+  </si>
+  <si>
+    <t>EGC.Bases</t>
+  </si>
+  <si>
+    <t>EGC.Movimentos</t>
+  </si>
+  <si>
+    <t>EGC.Parâmetros</t>
+  </si>
+  <si>
+    <t>Formal design code according to the EGC technique</t>
+  </si>
+  <si>
+    <t>Valor Z. Coordenada Z.</t>
+  </si>
+  <si>
+    <t>Valor desplazado. Valor de distancia de una traslación</t>
+  </si>
+  <si>
+    <t>Valor angular de una transformada de espín o rotación</t>
+  </si>
+  <si>
+    <t>Valor escalar de una transformación que cambia la escala</t>
+  </si>
+  <si>
+    <t>Punto 1 que define un eje de simetría</t>
+  </si>
+  <si>
+    <t>Punto 2 que define un eje de simetría</t>
+  </si>
+  <si>
+    <t>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</t>
+  </si>
+  <si>
+    <t>Código formal de diseño según la técnica EGC</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
   </si>
 </sst>
 </file>
@@ -2102,7 +2156,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2223,6 +2277,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2275,7 +2335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2462,19 +2522,26 @@
     <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2511,6 +2578,21 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2518,6 +2600,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2837,15 +2937,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -2853,10 +2953,10 @@
         <v>50</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -2864,21 +2964,21 @@
         <v>76</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -2886,10 +2986,10 @@
         <v>62</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -2898,10 +2998,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -2910,10 +3010,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -2921,21 +3021,21 @@
         <v>63</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -2943,10 +3043,10 @@
         <v>65</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -2954,10 +3054,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -2965,10 +3065,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -2976,10 +3076,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -2987,10 +3087,10 @@
         <v>38</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -2998,10 +3098,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3009,10 +3109,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3020,68 +3120,68 @@
         <v>38</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46244.67327013889</v>
+        <v>46253.790878125001</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="45" t="s">
-        <v>109</v>
-      </c>
       <c r="C19" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="45" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="45" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3089,10 +3189,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3100,41 +3200,41 @@
         <v>38</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3145,36 +3245,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC17"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="76" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="88.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="87.42578125" style="60" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.4609375" customWidth="1"/>
+    <col min="3" max="3" width="5.61328125" customWidth="1"/>
+    <col min="4" max="4" width="7.61328125" customWidth="1"/>
+    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.07421875" customWidth="1"/>
+    <col min="7" max="10" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.07421875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.23046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="54.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.23046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="62.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.07421875" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.765625" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.07421875" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.4609375" style="60" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3" style="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3226,55 +3328,61 @@
       <c r="Q1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="U1" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="V1" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="W1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="63" t="s">
+      <c r="X1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="Y1" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA1" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB1" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC1" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="Z1" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA1" s="41" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="61">
         <v>2</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G2" s="56" t="s">
         <v>1</v>
@@ -3297,76 +3405,81 @@
       </c>
       <c r="M2" s="51" t="str">
         <f t="shared" ref="M2:O16" si="1">_xlfn.CONCAT("", D2)</f>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N2" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Parâmetro.Geométrico</v>
+        <v>EGC.Parâmetros</v>
       </c>
       <c r="O2" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valor.X</v>
       </c>
       <c r="P2" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q2" s="51" t="str">
-        <f t="shared" ref="Q2:Q10" si="2">_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Valor de X. Coordenada X.</v>
+        <v>148</v>
+      </c>
+      <c r="Q2" s="51" t="s">
+        <v>148</v>
       </c>
       <c r="R2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="42" t="str">
-        <f t="shared" ref="S2:U16" si="3">SUBSTITUTE(C2, "_", " ")</f>
+        <v>157</v>
+      </c>
+      <c r="S2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="42" t="str">
+        <f t="shared" ref="T2:V16" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="T2" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U2" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V2" s="42" t="s">
+      <c r="U2" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V2" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Parâmetros</v>
+      </c>
+      <c r="W2" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="62" t="str">
-        <f t="shared" ref="W2:W16" si="4">CONCATENATE("Key-EGC-",A2)</f>
+      <c r="X2" s="62" t="str">
+        <f t="shared" ref="X2:X16" si="3">CONCATENATE("Key-EGC-",A2)</f>
         <v>Key-EGC-2</v>
       </c>
-      <c r="X2" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y2" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA2" s="42" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB2" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC2" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="61">
         <v>3</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G3" s="56" t="s">
         <v>1</v>
@@ -3389,76 +3502,81 @@
       </c>
       <c r="M3" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N3" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Parâmetro.Geométrico</v>
+        <v>EGC.Parâmetros</v>
       </c>
       <c r="O3" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Y</v>
       </c>
       <c r="P3" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q3" s="51" t="str">
+        <v>147</v>
+      </c>
+      <c r="Q3" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="R3" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="S3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Valor de Y. Coordenada Y.</v>
-      </c>
-      <c r="R3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U3" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V3" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Parâmetros</v>
+      </c>
+      <c r="W3" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T3" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U3" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V3" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W3" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-3</v>
       </c>
-      <c r="X3" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y3" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z3" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA3" s="42" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB3" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC3" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="61">
         <v>4</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G4" s="56" t="s">
         <v>1</v>
@@ -3481,76 +3599,81 @@
       </c>
       <c r="M4" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N4" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Parâmetro.Geométrico</v>
+        <v>EGC.Parâmetros</v>
       </c>
       <c r="O4" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Z</v>
       </c>
       <c r="P4" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q4" s="51" t="str">
+        <v>149</v>
+      </c>
+      <c r="Q4" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="S4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Valor Z. Coordenada Z.</v>
-      </c>
-      <c r="R4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U4" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V4" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Parâmetros</v>
+      </c>
+      <c r="W4" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X4" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T4" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U4" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V4" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W4" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-4</v>
       </c>
-      <c r="X4" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y4" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z4" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA4" s="42" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB4" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC4" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="61">
         <v>5</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G5" s="56" t="s">
         <v>1</v>
@@ -3573,76 +3696,81 @@
       </c>
       <c r="M5" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N5" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Parâmetro.Geométrico</v>
+        <v>EGC.Parâmetros</v>
       </c>
       <c r="O5" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Distância</v>
       </c>
       <c r="P5" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q5" s="51" t="str">
+        <v>146</v>
+      </c>
+      <c r="Q5" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="R5" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="S5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Valor desplazado. Valor de distancia de una traslación</v>
-      </c>
-      <c r="R5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U5" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V5" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Parâmetros</v>
+      </c>
+      <c r="W5" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X5" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T5" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U5" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V5" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W5" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-5</v>
       </c>
-      <c r="X5" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y5" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z5" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA5" s="42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB5" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC5" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="61">
         <v>6</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G6" s="56" t="s">
         <v>1</v>
@@ -3665,76 +3793,81 @@
       </c>
       <c r="M6" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N6" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Parâmetro.Geométrico</v>
+        <v>EGC.Parâmetros</v>
       </c>
       <c r="O6" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Angular</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q6" s="51" t="str">
+        <v>145</v>
+      </c>
+      <c r="Q6" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="R6" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="S6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Valor angular de una transformada de espín o rotación</v>
-      </c>
-      <c r="R6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U6" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V6" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Parâmetros</v>
+      </c>
+      <c r="W6" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X6" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T6" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U6" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V6" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W6" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-6</v>
       </c>
-      <c r="X6" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y6" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z6" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA6" s="42" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB6" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC6" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61">
         <v>7</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G7" s="56" t="s">
         <v>1</v>
@@ -3757,76 +3890,81 @@
       </c>
       <c r="M7" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N7" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Parâmetro.Geométrico</v>
+        <v>EGC.Parâmetros</v>
       </c>
       <c r="O7" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Escalar</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q7" s="51" t="str">
+        <v>144</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="R7" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="S7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Valor escalar de una transformación que cambia la escala</v>
-      </c>
-      <c r="R7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U7" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V7" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Parâmetros</v>
+      </c>
+      <c r="W7" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X7" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T7" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U7" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V7" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W7" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-7</v>
       </c>
-      <c r="X7" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y7" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z7" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA7" s="42" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB7" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC7" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="61">
         <v>8</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G8" s="56" t="s">
         <v>1</v>
@@ -3849,76 +3987,81 @@
       </c>
       <c r="M8" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N8" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Bases.Geométricas</v>
+        <v>EGC.Bases</v>
       </c>
       <c r="O8" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q8" s="51" t="str">
+        <v>140</v>
+      </c>
+      <c r="Q8" s="51" t="s">
+        <v>229</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Punto 1 que define un eje de simetría</v>
-      </c>
-      <c r="R8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U8" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V8" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Bases</v>
+      </c>
+      <c r="W8" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X8" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T8" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U8" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V8" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W8" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-8</v>
       </c>
-      <c r="X8" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y8" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z8" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA8" s="42" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB8" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC8" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="61">
         <v>9</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G9" s="56" t="s">
         <v>1</v>
@@ -3941,76 +4084,81 @@
       </c>
       <c r="M9" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N9" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Bases.Geométricas</v>
+        <v>EGC.Bases</v>
       </c>
       <c r="O9" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q9" s="51" t="str">
+        <v>141</v>
+      </c>
+      <c r="Q9" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="R9" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="S9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Punto 2 que define un eje de simetría</v>
-      </c>
-      <c r="R9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U9" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V9" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Bases</v>
+      </c>
+      <c r="W9" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X9" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T9" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U9" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V9" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W9" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-9</v>
       </c>
-      <c r="X9" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y9" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z9" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA9" s="42" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB9" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC9" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="61">
         <v>10</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G10" s="56" t="s">
         <v>1</v>
@@ -4033,76 +4181,81 @@
       </c>
       <c r="M10" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N10" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Bases.Geométricas</v>
+        <v>EGC.Bases</v>
       </c>
       <c r="O10" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Base</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q10" s="51" t="str">
+        <v>142</v>
+      </c>
+      <c r="Q10" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="R10" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="S10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
-      </c>
-      <c r="R10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="42" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="U10" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V10" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Bases</v>
+      </c>
+      <c r="W10" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X10" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T10" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U10" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V10" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W10" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-10</v>
       </c>
-      <c r="X10" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y10" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z10" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA10" s="42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB10" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC10" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="61">
         <v>11</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G11" s="56" t="s">
         <v>1</v>
@@ -4125,166 +4278,178 @@
       </c>
       <c r="M11" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N11" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Bases.Geométricas</v>
+        <v>EGC.Bases</v>
       </c>
       <c r="O11" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Destino</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q11" s="51" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="R11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="42" t="str">
+        <v>166</v>
+      </c>
+      <c r="S11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Formantes</v>
+      </c>
+      <c r="U11" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V11" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Bases</v>
+      </c>
+      <c r="W11" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X11" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T11" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U11" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V11" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W11" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-11</v>
       </c>
-      <c r="X11" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y11" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z11" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA11" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB11" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC11" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="61">
         <v>12</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="F12" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" s="51" t="str">
+        <f t="shared" ref="L12" si="4">_xlfn.CONCAT(C12)</f>
+        <v>Formantes</v>
+      </c>
+      <c r="M12" s="51" t="str">
+        <f t="shared" ref="M12" si="5">_xlfn.CONCAT("", D12)</f>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="N12" s="51" t="str">
+        <f t="shared" ref="N12" si="6">_xlfn.CONCAT("", E12)</f>
+        <v>EGC.Movimentos</v>
+      </c>
+      <c r="O12" s="51" t="str">
+        <f t="shared" ref="O12" si="7">_xlfn.CONCAT("", F12)</f>
+        <v>Translação.XYZ</v>
+      </c>
+      <c r="P12" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q12" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="R12" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="G12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="56" t="s">
-        <v>212</v>
-      </c>
-      <c r="L12" s="51" t="str">
-        <f t="shared" ref="L12" si="5">_xlfn.CONCAT(C12)</f>
+      <c r="S12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="42" t="str">
+        <f t="shared" ref="T12" si="8">SUBSTITUTE(C12, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="M12" s="51" t="str">
-        <f t="shared" ref="M12" si="6">_xlfn.CONCAT("", D12)</f>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N12" s="51" t="str">
-        <f t="shared" ref="N12" si="7">_xlfn.CONCAT("", E12)</f>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O12" s="51" t="str">
-        <f t="shared" ref="O12" si="8">_xlfn.CONCAT("", F12)</f>
-        <v>Translação.XYZ</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q12" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="R12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="42" t="str">
-        <f t="shared" ref="S12" si="9">SUBSTITUTE(C12, "_", " ")</f>
-        <v>Formantes</v>
-      </c>
-      <c r="T12" s="42" t="str">
-        <f t="shared" ref="T12" si="10">SUBSTITUTE(D12, "_", " ")</f>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U12" s="52" t="str">
-        <f t="shared" ref="U12" si="11">SUBSTITUTE(E12, "_", " ")</f>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V12" s="42" t="s">
+      <c r="U12" s="42" t="str">
+        <f t="shared" ref="U12" si="9">SUBSTITUTE(D12, "_", " ")</f>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V12" s="52" t="str">
+        <f t="shared" ref="V12" si="10">SUBSTITUTE(E12, "_", " ")</f>
+        <v>EGC.Movimentos</v>
+      </c>
+      <c r="W12" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W12" s="62" t="str">
-        <f t="shared" si="4"/>
+      <c r="X12" s="62" t="str">
+        <f t="shared" si="3"/>
         <v>Key-EGC-12</v>
       </c>
-      <c r="X12" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y12" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z12" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA12" s="42" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB12" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC12" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="61">
         <v>13</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G13" s="56" t="s">
         <v>1</v>
@@ -4299,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="56" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L13" s="51" t="str">
         <f t="shared" si="0"/>
@@ -4307,75 +4472,81 @@
       </c>
       <c r="M13" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N13" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Movimento.Geométrico</v>
+        <v>EGC.Movimentos</v>
       </c>
       <c r="O13" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Translação.Polar</v>
       </c>
       <c r="P13" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="R13" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="Q13" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="R13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="42" t="str">
+      <c r="S13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Formantes</v>
+      </c>
+      <c r="U13" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V13" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Movimentos</v>
+      </c>
+      <c r="W13" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X13" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T13" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U13" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V13" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W13" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-13</v>
       </c>
-      <c r="X13" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y13" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z13" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA13" s="42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB13" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC13" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="61">
         <v>14</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G14" s="56" t="s">
         <v>1</v>
@@ -4390,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="56" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="L14" s="51" t="str">
         <f t="shared" si="0"/>
@@ -4398,76 +4569,82 @@
       </c>
       <c r="M14" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N14" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Movimento.Geométrico</v>
+        <v>EGC.Movimentos</v>
       </c>
       <c r="O14" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Giro</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q14" s="51" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="R14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="42" t="str">
+        <v>167</v>
+      </c>
+      <c r="S14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Formantes</v>
+      </c>
+      <c r="U14" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V14" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Movimentos</v>
+      </c>
+      <c r="W14" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X14" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T14" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U14" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V14" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W14" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-14</v>
       </c>
-      <c r="X14" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y14" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z14" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA14" s="42" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB14" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC14" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="61">
         <v>15</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E15" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="46" t="s">
-        <v>116</v>
-      </c>
       <c r="G15" s="56" t="s">
         <v>1</v>
       </c>
@@ -4481,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="56" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L15" s="51" t="str">
         <f t="shared" si="0"/>
@@ -4489,75 +4666,81 @@
       </c>
       <c r="M15" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N15" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Movimento.Geométrico</v>
+        <v>EGC.Movimentos</v>
       </c>
       <c r="O15" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Escalar</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q15" s="51" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="R15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="42" t="str">
+        <v>168</v>
+      </c>
+      <c r="S15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Formantes</v>
+      </c>
+      <c r="U15" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V15" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Movimentos</v>
+      </c>
+      <c r="W15" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X15" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T15" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U15" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V15" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W15" s="62" t="str">
-        <f t="shared" si="4"/>
         <v>Key-EGC-15</v>
       </c>
-      <c r="X15" s="42" t="s">
-        <v>1</v>
-      </c>
       <c r="Y15" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="Z15" s="42" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="AA15" s="42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="AB15" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC15" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="61">
         <v>16</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G16" s="56" t="s">
         <v>1</v>
@@ -4572,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="56" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="L16" s="51" t="str">
         <f t="shared" si="0"/>
@@ -4580,67 +4763,186 @@
       </c>
       <c r="M16" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Elementos.TGB</v>
+        <v>Elementos.EGC</v>
       </c>
       <c r="N16" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Movimento.Geométrico</v>
+        <v>EGC.Movimentos</v>
       </c>
       <c r="O16" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Reflexão</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q16" s="51" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="R16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="42" t="str">
+        <v>169</v>
+      </c>
+      <c r="S16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Formantes</v>
+      </c>
+      <c r="U16" s="42" t="str">
+        <f t="shared" si="2"/>
+        <v>Elementos.EGC</v>
+      </c>
+      <c r="V16" s="52" t="str">
+        <f t="shared" si="2"/>
+        <v>EGC.Movimentos</v>
+      </c>
+      <c r="W16" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="X16" s="62" t="str">
         <f t="shared" si="3"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T16" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U16" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V16" s="42" t="s">
+        <v>Key-EGC-16</v>
+      </c>
+      <c r="Y16" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z16" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA16" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB16" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC16" s="42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="61">
+        <v>17</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="G17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="52" t="str">
+        <f t="shared" ref="L17:O17" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
+        <v>Morfológico</v>
+      </c>
+      <c r="M17" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Morfologias</v>
+      </c>
+      <c r="N17" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Códificação Formal</v>
+      </c>
+      <c r="O17" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Código De Forma</v>
+      </c>
+      <c r="P17" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q17" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="R17" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="S17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="42" t="str">
+        <f t="shared" ref="T17:V17" si="12">SUBSTITUTE(C17, ".", " ")</f>
+        <v>Morfológico</v>
+      </c>
+      <c r="U17" s="42" t="str">
+        <f t="shared" si="12"/>
+        <v>Morfologias</v>
+      </c>
+      <c r="V17" s="42" t="str">
+        <f t="shared" si="12"/>
+        <v>Códificação Formal</v>
+      </c>
+      <c r="W17" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W16" s="62" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-EGC-16</v>
-      </c>
-      <c r="X16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="42" t="s">
-        <v>174</v>
+      <c r="X17" s="62" t="str">
+        <f t="shared" ref="X17" si="13">CONCATENATE("Key-MAT-",A17)</f>
+        <v>Key-MAT-17</v>
+      </c>
+      <c r="Y17" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z17" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA17" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB17" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC17" s="42" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B16">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B17">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F16">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q17">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R17">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4648,15 +4950,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
@@ -4721,7 +5023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -4786,7 +5088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -4854,7 +5156,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4867,14 +5169,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -4885,7 +5187,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -4898,7 +5200,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4910,36 +5212,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="59" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.15234375" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.15234375" customWidth="1"/>
+    <col min="8" max="8" width="4.07421875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.23046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.23046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="39" t="s">
         <v>91</v>
       </c>
@@ -5016,15 +5317,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="26">
         <v>2</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>1</v>
@@ -5042,28 +5343,28 @@
         <v>95</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K2" s="47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M2" s="58">
         <v>1.05</v>
       </c>
       <c r="N2" s="37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O2" s="58">
         <v>1.05</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Q2" s="58">
         <v>0</v>
@@ -5093,15 +5394,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="26">
         <v>3</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>1</v>
@@ -5119,46 +5420,46 @@
         <v>95</v>
       </c>
       <c r="I3" s="38" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K3" s="47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M3" s="58">
         <v>1.05</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O3" s="58">
         <v>1.05</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Q3" s="58">
         <v>0</v>
       </c>
       <c r="R3" s="37" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="S3" s="58">
         <v>5.2</v>
       </c>
       <c r="T3" s="37" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="U3" s="58">
         <v>0</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="W3" s="58">
         <v>0</v>
@@ -5170,15 +5471,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="26">
         <v>4</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" s="49" t="s">
         <v>1</v>
@@ -5196,28 +5497,28 @@
         <v>95</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K4" s="47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M4" s="58">
         <v>2.0499999999999998</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O4" s="58">
         <v>2.0499999999999998</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Q4" s="58">
         <v>0</v>
@@ -5241,21 +5542,21 @@
         <v>1</v>
       </c>
       <c r="X4" s="37" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Y4" s="47">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="26">
         <v>5</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D5" s="49" t="s">
         <v>1</v>
@@ -5273,28 +5574,28 @@
         <v>95</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J5" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="K5" s="47" t="s">
-        <v>124</v>
-      </c>
       <c r="L5" s="37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M5" s="58">
         <v>3.05</v>
       </c>
       <c r="N5" s="37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O5" s="58">
         <v>3.05</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Q5" s="58">
         <v>0</v>
@@ -5318,21 +5619,21 @@
         <v>1</v>
       </c>
       <c r="X5" s="37" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y5" s="47">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="26">
         <v>6</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>1</v>
@@ -5350,46 +5651,46 @@
         <v>95</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K6" s="47" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="M6" s="58">
         <v>4.05</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O6" s="58">
         <v>4.05</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Q6" s="58">
         <v>0</v>
       </c>
       <c r="R6" s="36" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="S6" s="58">
         <v>14.05</v>
       </c>
       <c r="T6" s="36" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="U6" s="58">
         <v>14.05</v>
       </c>
       <c r="V6" s="36" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="W6" s="58">
         <v>0</v>
@@ -5401,15 +5702,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="26">
         <v>7</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>1</v>
@@ -5427,7 +5728,7 @@
         <v>95</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J7" s="37" t="s">
         <v>1</v>
@@ -5478,15 +5779,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="26">
         <v>8</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>1</v>
@@ -5504,7 +5805,7 @@
         <v>95</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J8" s="37" t="s">
         <v>1</v>
@@ -5555,33 +5856,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="26">
         <v>9</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E9" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="50" t="s">
         <v>133</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>136</v>
       </c>
       <c r="H9" s="36" t="s">
         <v>95</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J9" s="37" t="s">
         <v>1</v>
@@ -5632,33 +5933,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="26">
         <v>10</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>95</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>1</v>
@@ -5709,15 +6010,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="26">
         <v>11</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>1</v>
@@ -5735,7 +6036,7 @@
         <v>95</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J11" s="37" t="s">
         <v>1</v>
@@ -5786,15 +6087,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="26">
         <v>12</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>1</v>
@@ -5812,7 +6113,7 @@
         <v>95</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>1</v>
@@ -5857,21 +6158,21 @@
         <v>1</v>
       </c>
       <c r="X12" s="37" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="Y12" s="47" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="26">
         <v>13</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>1</v>
@@ -5889,7 +6190,7 @@
         <v>95</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J13" s="37" t="s">
         <v>1</v>
@@ -5934,21 +6235,21 @@
         <v>1</v>
       </c>
       <c r="X13" s="37" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Y13" s="47">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="26">
         <v>14</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>1</v>
@@ -5966,7 +6267,7 @@
         <v>95</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>1</v>
@@ -6011,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="37" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Y14" s="47">
         <v>60</v>
@@ -6020,12 +6321,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B14 H1:I14">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6035,14 +6336,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6050,7 +6351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6058,7 +6359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6066,7 +6367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6074,7 +6375,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6082,7 +6383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6090,7 +6391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6098,7 +6399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6106,7 +6407,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6114,7 +6415,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6122,7 +6423,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6130,7 +6431,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6138,7 +6439,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6146,7 +6447,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6154,7 +6455,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Genetica.xlsx
+++ b/Versão5/PRO/Ontologia_Genetica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DE17C2-D888-4071-905A-D7666D59D5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA316213-4E78-410D-A613-0F4A542B81A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="266">
   <si>
     <t>Key</t>
   </si>
@@ -1972,7 +1972,94 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -2156,7 +2243,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2283,6 +2370,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2335,7 +2452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2408,9 +2525,6 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2471,26 +2585,17 @@
     <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2537,11 +2642,171 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2590,6 +2855,16 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2937,59 +3212,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -2997,11 +3272,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3009,223 +3284,223 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46253.790878125001</v>
-      </c>
-      <c r="C18" s="43" t="s">
+        <v>46259.680473263892</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="45" t="str">
+      <c r="B20" s="44" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="45" t="str">
+      <c r="B21" s="44" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>99</v>
       </c>
@@ -3233,7 +3508,7 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="42" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3245,38 +3520,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC17"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC18"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.4609375" customWidth="1"/>
-    <col min="3" max="3" width="5.61328125" customWidth="1"/>
-    <col min="4" max="4" width="7.61328125" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.07421875" customWidth="1"/>
-    <col min="7" max="10" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="10" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.07421875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.23046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="54.3828125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.23046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="62.84375" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.07421875" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.765625" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.07421875" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.3828125" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.3828125" style="60" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.4609375" style="60" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3" style="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="54.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="62.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="56" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.140625" style="56" customWidth="1"/>
+    <col min="21" max="21" width="7.85546875" style="56" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" style="56" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="5.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3" style="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3295,19 +3569,19 @@
       <c r="F1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="51" t="s">
         <v>43</v>
       </c>
       <c r="L1" s="22" t="s">
@@ -3328,7 +3602,7 @@
       <c r="Q1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="40" t="s">
         <v>98</v>
       </c>
       <c r="S1" s="22" t="s">
@@ -3346,7 +3620,7 @@
       <c r="W1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="63" t="s">
+      <c r="X1" s="59" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="22" t="s">
@@ -3365,11 +3639,11 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="61">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="57">
         <v>2</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C2" s="24" t="s">
@@ -3381,92 +3655,92 @@
       <c r="E2" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="51" t="str">
+      <c r="G2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="48" t="str">
         <f t="shared" ref="L2:L16" si="0">_xlfn.CONCAT(C2)</f>
         <v>Formantes</v>
       </c>
-      <c r="M2" s="51" t="str">
+      <c r="M2" s="48" t="str">
         <f t="shared" ref="M2:O16" si="1">_xlfn.CONCAT("", D2)</f>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N2" s="51" t="str">
+      <c r="N2" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O2" s="51" t="str">
+      <c r="O2" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Valor.X</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="R2" s="42" t="s">
+      <c r="R2" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="S2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="42" t="str">
+      <c r="S2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="41" t="str">
         <f t="shared" ref="T2:V16" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="U2" s="42" t="str">
+      <c r="U2" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V2" s="52" t="str">
+      <c r="V2" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="W2" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X2" s="62" t="str">
-        <f t="shared" ref="X2:X16" si="3">CONCATENATE("Key-EGC-",A2)</f>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X18" si="3">CONCATENATE("Key-EGC-",A2)</f>
         <v>Key-EGC-2</v>
       </c>
-      <c r="Y2" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z2" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA2" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB2" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC2" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="61">
+      <c r="Y2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="57">
         <v>3</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C3" s="24" t="s">
@@ -3478,92 +3752,92 @@
       <c r="E3" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="51" t="str">
+      <c r="G3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M3" s="51" t="str">
+      <c r="M3" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N3" s="51" t="str">
+      <c r="N3" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O3" s="51" t="str">
+      <c r="O3" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Y</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="R3" s="42" t="s">
+      <c r="R3" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="42" t="str">
+      <c r="S3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U3" s="42" t="str">
+      <c r="U3" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V3" s="52" t="str">
+      <c r="V3" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W3" s="42" t="s">
+      <c r="W3" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X3" s="62" t="str">
+      <c r="X3" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-3</v>
       </c>
-      <c r="Y3" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z3" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA3" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB3" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC3" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="61">
+      <c r="Y3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="57">
         <v>4</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C4" s="24" t="s">
@@ -3575,92 +3849,92 @@
       <c r="E4" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="51" t="str">
+      <c r="G4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M4" s="51" t="str">
+      <c r="M4" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N4" s="51" t="str">
+      <c r="N4" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O4" s="51" t="str">
+      <c r="O4" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Z</v>
       </c>
-      <c r="P4" s="51" t="s">
+      <c r="P4" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="Q4" s="51" t="s">
+      <c r="Q4" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="R4" s="42" t="s">
+      <c r="R4" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="S4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="42" t="str">
+      <c r="S4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U4" s="42" t="str">
+      <c r="U4" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V4" s="52" t="str">
+      <c r="V4" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W4" s="42" t="s">
+      <c r="W4" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X4" s="62" t="str">
+      <c r="X4" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-4</v>
       </c>
-      <c r="Y4" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z4" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA4" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB4" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC4" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="61">
+      <c r="Y4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="57">
         <v>5</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C5" s="24" t="s">
@@ -3672,92 +3946,92 @@
       <c r="E5" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="G5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="51" t="str">
+      <c r="G5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M5" s="51" t="str">
+      <c r="M5" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N5" s="51" t="str">
+      <c r="N5" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O5" s="51" t="str">
+      <c r="O5" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Distância</v>
       </c>
-      <c r="P5" s="51" t="s">
+      <c r="P5" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="Q5" s="51" t="s">
+      <c r="Q5" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="R5" s="42" t="s">
+      <c r="R5" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="S5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="42" t="str">
+      <c r="S5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U5" s="42" t="str">
+      <c r="U5" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V5" s="52" t="str">
+      <c r="V5" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W5" s="42" t="s">
+      <c r="W5" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X5" s="62" t="str">
+      <c r="X5" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-5</v>
       </c>
-      <c r="Y5" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z5" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA5" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB5" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC5" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="61">
+      <c r="Y5" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57">
         <v>6</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C6" s="24" t="s">
@@ -3769,92 +4043,92 @@
       <c r="E6" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="G6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="51" t="str">
+      <c r="G6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M6" s="51" t="str">
+      <c r="M6" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N6" s="51" t="str">
+      <c r="N6" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O6" s="51" t="str">
+      <c r="O6" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Angular</v>
       </c>
-      <c r="P6" s="51" t="s">
+      <c r="P6" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="Q6" s="51" t="s">
+      <c r="Q6" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="R6" s="42" t="s">
+      <c r="R6" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="S6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="42" t="str">
+      <c r="S6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U6" s="42" t="str">
+      <c r="U6" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V6" s="52" t="str">
+      <c r="V6" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W6" s="42" t="s">
+      <c r="W6" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X6" s="62" t="str">
+      <c r="X6" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-6</v>
       </c>
-      <c r="Y6" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z6" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA6" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB6" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC6" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="61">
+      <c r="Y6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="57">
         <v>7</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C7" s="24" t="s">
@@ -3866,92 +4140,92 @@
       <c r="E7" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="51" t="str">
+      <c r="G7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M7" s="51" t="str">
+      <c r="M7" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N7" s="51" t="str">
+      <c r="N7" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O7" s="51" t="str">
+      <c r="O7" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Escalar</v>
       </c>
-      <c r="P7" s="51" t="s">
+      <c r="P7" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="Q7" s="51" t="s">
+      <c r="Q7" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="S7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="42" t="str">
+      <c r="S7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U7" s="42" t="str">
+      <c r="U7" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V7" s="52" t="str">
+      <c r="V7" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W7" s="42" t="s">
+      <c r="W7" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X7" s="62" t="str">
+      <c r="X7" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-7</v>
       </c>
-      <c r="Y7" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z7" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA7" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB7" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC7" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="61">
+      <c r="Y7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="57">
         <v>8</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C8" s="24" t="s">
@@ -3963,92 +4237,92 @@
       <c r="E8" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="51" t="str">
+      <c r="G8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M8" s="51" t="str">
+      <c r="M8" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N8" s="51" t="str">
+      <c r="N8" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O8" s="51" t="str">
+      <c r="O8" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Eixo1</v>
       </c>
-      <c r="P8" s="51" t="s">
+      <c r="P8" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="Q8" s="51" t="s">
+      <c r="Q8" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="R8" s="42" t="s">
+      <c r="R8" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="S8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="42" t="str">
+      <c r="S8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U8" s="42" t="str">
+      <c r="U8" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V8" s="52" t="str">
+      <c r="V8" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W8" s="42" t="s">
+      <c r="W8" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X8" s="62" t="str">
+      <c r="X8" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-8</v>
       </c>
-      <c r="Y8" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z8" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA8" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB8" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC8" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="61">
+      <c r="Y8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="57">
         <v>9</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C9" s="24" t="s">
@@ -4060,92 +4334,92 @@
       <c r="E9" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="51" t="str">
+      <c r="G9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M9" s="51" t="str">
+      <c r="M9" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N9" s="51" t="str">
+      <c r="N9" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O9" s="51" t="str">
+      <c r="O9" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Eixo2</v>
       </c>
-      <c r="P9" s="51" t="s">
+      <c r="P9" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="Q9" s="51" t="s">
+      <c r="Q9" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="R9" s="42" t="s">
+      <c r="R9" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="S9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="42" t="str">
+      <c r="S9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U9" s="42" t="str">
+      <c r="U9" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V9" s="52" t="str">
+      <c r="V9" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W9" s="42" t="s">
+      <c r="W9" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X9" s="62" t="str">
+      <c r="X9" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-9</v>
       </c>
-      <c r="Y9" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z9" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA9" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB9" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC9" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="61">
+      <c r="Y9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="57">
         <v>10</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C10" s="24" t="s">
@@ -4157,92 +4431,92 @@
       <c r="E10" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="51" t="str">
+      <c r="G10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M10" s="51" t="str">
+      <c r="M10" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N10" s="51" t="str">
+      <c r="N10" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O10" s="51" t="str">
+      <c r="O10" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Base</v>
       </c>
-      <c r="P10" s="51" t="s">
+      <c r="P10" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="Q10" s="51" t="s">
+      <c r="Q10" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="R10" s="42" t="s">
+      <c r="R10" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="S10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="42" t="str">
+      <c r="S10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U10" s="42" t="str">
+      <c r="U10" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V10" s="52" t="str">
+      <c r="V10" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W10" s="42" t="s">
+      <c r="W10" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X10" s="62" t="str">
+      <c r="X10" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-10</v>
       </c>
-      <c r="Y10" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z10" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA10" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB10" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC10" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61">
+      <c r="Y10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="57">
         <v>11</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C11" s="24" t="s">
@@ -4254,92 +4528,92 @@
       <c r="E11" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="51" t="str">
+      <c r="G11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M11" s="51" t="str">
+      <c r="M11" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N11" s="51" t="str">
+      <c r="N11" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O11" s="51" t="str">
+      <c r="O11" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Destino</v>
       </c>
-      <c r="P11" s="51" t="s">
+      <c r="P11" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="Q11" s="51" t="s">
+      <c r="Q11" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="R11" s="42" t="s">
+      <c r="R11" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="S11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="42" t="str">
+      <c r="S11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U11" s="42" t="str">
+      <c r="U11" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V11" s="52" t="str">
+      <c r="V11" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W11" s="42" t="s">
+      <c r="W11" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X11" s="62" t="str">
+      <c r="X11" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-11</v>
       </c>
-      <c r="Y11" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z11" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA11" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB11" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC11" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="61">
+      <c r="Y11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="57">
         <v>12</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C12" s="24" t="s">
@@ -4351,92 +4625,92 @@
       <c r="E12" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="G12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="56" t="s">
+      <c r="G12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="L12" s="51" t="str">
+      <c r="L12" s="48" t="str">
         <f t="shared" ref="L12" si="4">_xlfn.CONCAT(C12)</f>
         <v>Formantes</v>
       </c>
-      <c r="M12" s="51" t="str">
+      <c r="M12" s="48" t="str">
         <f t="shared" ref="M12" si="5">_xlfn.CONCAT("", D12)</f>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N12" s="51" t="str">
+      <c r="N12" s="48" t="str">
         <f t="shared" ref="N12" si="6">_xlfn.CONCAT("", E12)</f>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O12" s="51" t="str">
+      <c r="O12" s="48" t="str">
         <f t="shared" ref="O12" si="7">_xlfn.CONCAT("", F12)</f>
         <v>Translação.XYZ</v>
       </c>
-      <c r="P12" s="51" t="s">
+      <c r="P12" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="Q12" s="51" t="s">
+      <c r="Q12" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="R12" s="42" t="s">
+      <c r="R12" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="S12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="42" t="str">
+      <c r="S12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="41" t="str">
         <f t="shared" ref="T12" si="8">SUBSTITUTE(C12, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="U12" s="42" t="str">
+      <c r="U12" s="41" t="str">
         <f t="shared" ref="U12" si="9">SUBSTITUTE(D12, "_", " ")</f>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V12" s="52" t="str">
+      <c r="V12" s="49" t="str">
         <f t="shared" ref="V12" si="10">SUBSTITUTE(E12, "_", " ")</f>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W12" s="42" t="s">
+      <c r="W12" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X12" s="62" t="str">
+      <c r="X12" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-12</v>
       </c>
-      <c r="Y12" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z12" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA12" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB12" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC12" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="61">
+      <c r="Y12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="57">
         <v>13</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -4448,92 +4722,92 @@
       <c r="E13" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="56" t="s">
+      <c r="G13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="52" t="s">
         <v>211</v>
       </c>
-      <c r="L13" s="51" t="str">
+      <c r="L13" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M13" s="51" t="str">
+      <c r="M13" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N13" s="51" t="str">
+      <c r="N13" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O13" s="51" t="str">
+      <c r="O13" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Translação.Polar</v>
       </c>
-      <c r="P13" s="51" t="s">
+      <c r="P13" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="Q13" s="51" t="s">
+      <c r="Q13" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="R13" s="42" t="s">
+      <c r="R13" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="S13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="42" t="str">
+      <c r="S13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U13" s="42" t="str">
+      <c r="U13" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V13" s="52" t="str">
+      <c r="V13" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W13" s="42" t="s">
+      <c r="W13" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X13" s="62" t="str">
+      <c r="X13" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-13</v>
       </c>
-      <c r="Y13" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z13" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA13" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB13" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC13" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="61">
+      <c r="Y13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="57">
         <v>14</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C14" s="24" t="s">
@@ -4545,92 +4819,92 @@
       <c r="E14" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="56" t="s">
+      <c r="G14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="L14" s="51" t="str">
+      <c r="L14" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M14" s="51" t="str">
+      <c r="M14" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N14" s="51" t="str">
+      <c r="N14" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O14" s="51" t="str">
+      <c r="O14" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Giro</v>
       </c>
-      <c r="P14" s="51" t="s">
+      <c r="P14" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="Q14" s="51" t="s">
+      <c r="Q14" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="R14" s="42" t="s">
+      <c r="R14" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="S14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="42" t="str">
+      <c r="S14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U14" s="42" t="str">
+      <c r="U14" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V14" s="52" t="str">
+      <c r="V14" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W14" s="42" t="s">
+      <c r="W14" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X14" s="62" t="str">
+      <c r="X14" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-14</v>
       </c>
-      <c r="Y14" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z14" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA14" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB14" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC14" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="61">
+      <c r="Y14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="57">
         <v>15</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C15" s="24" t="s">
@@ -4642,92 +4916,92 @@
       <c r="E15" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="56" t="s">
+      <c r="G15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="L15" s="51" t="str">
+      <c r="L15" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M15" s="51" t="str">
+      <c r="M15" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N15" s="51" t="str">
+      <c r="N15" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O15" s="51" t="str">
+      <c r="O15" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Escalar</v>
       </c>
-      <c r="P15" s="51" t="s">
+      <c r="P15" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="Q15" s="51" t="s">
+      <c r="Q15" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="R15" s="42" t="s">
+      <c r="R15" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="S15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="42" t="str">
+      <c r="S15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U15" s="42" t="str">
+      <c r="U15" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V15" s="52" t="str">
+      <c r="V15" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W15" s="42" t="s">
+      <c r="W15" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X15" s="62" t="str">
+      <c r="X15" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-15</v>
       </c>
-      <c r="Y15" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z15" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA15" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB15" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC15" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="61">
+      <c r="Y15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="57">
         <v>16</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="50" t="s">
         <v>212</v>
       </c>
       <c r="C16" s="24" t="s">
@@ -4739,203 +5013,303 @@
       <c r="E16" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="56" t="s">
+      <c r="G16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="52" t="s">
         <v>210</v>
       </c>
-      <c r="L16" s="51" t="str">
+      <c r="L16" s="48" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M16" s="51" t="str">
+      <c r="M16" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N16" s="51" t="str">
+      <c r="N16" s="48" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O16" s="51" t="str">
+      <c r="O16" s="48" t="str">
         <f t="shared" si="1"/>
         <v>Reflexão</v>
       </c>
-      <c r="P16" s="51" t="s">
+      <c r="P16" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="Q16" s="51" t="s">
+      <c r="Q16" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="R16" s="42" t="s">
+      <c r="R16" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="S16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="42" t="str">
+      <c r="S16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U16" s="42" t="str">
+      <c r="U16" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V16" s="52" t="str">
+      <c r="V16" s="49" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W16" s="42" t="s">
+      <c r="W16" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X16" s="62" t="str">
+      <c r="X16" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-16</v>
       </c>
-      <c r="Y16" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z16" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA16" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB16" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC16" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="61">
+      <c r="Y16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="57">
         <v>17</v>
       </c>
-      <c r="B17" s="64" t="s">
+      <c r="B17" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="65" t="s">
+      <c r="D17" s="61" t="s">
         <v>218</v>
       </c>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="61" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="65" t="s">
+      <c r="F17" s="61" t="s">
         <v>216</v>
       </c>
-      <c r="G17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="52" t="str">
-        <f t="shared" ref="L17:O17" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
+      <c r="G17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="49" t="str">
+        <f t="shared" ref="L17:O18" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
         <v>Morfológico</v>
       </c>
-      <c r="M17" s="52" t="str">
+      <c r="M17" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Morfologias</v>
       </c>
-      <c r="N17" s="52" t="str">
+      <c r="N17" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Códificação Formal</v>
       </c>
-      <c r="O17" s="52" t="str">
+      <c r="O17" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Código De Forma</v>
       </c>
-      <c r="P17" s="42" t="s">
+      <c r="P17" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="Q17" s="67" t="s">
+      <c r="Q17" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="R17" s="42" t="s">
+      <c r="R17" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="S17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="42" t="str">
-        <f t="shared" ref="T17:V17" si="12">SUBSTITUTE(C17, ".", " ")</f>
+      <c r="S17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="41" t="str">
+        <f t="shared" ref="T17:V18" si="12">SUBSTITUTE(C17, ".", " ")</f>
         <v>Morfológico</v>
       </c>
-      <c r="U17" s="42" t="str">
+      <c r="U17" s="41" t="str">
         <f t="shared" si="12"/>
         <v>Morfologias</v>
       </c>
-      <c r="V17" s="42" t="str">
+      <c r="V17" s="41" t="str">
         <f t="shared" si="12"/>
         <v>Códificação Formal</v>
       </c>
-      <c r="W17" s="42" t="s">
+      <c r="W17" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="X17" s="62" t="str">
-        <f t="shared" ref="X17" si="13">CONCATENATE("Key-MAT-",A17)</f>
-        <v>Key-MAT-17</v>
-      </c>
-      <c r="Y17" s="42" t="s">
+      <c r="X17" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-EGC-17</v>
+      </c>
+      <c r="Y17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="57">
+        <v>18</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="65" t="s">
         <v>236</v>
       </c>
-      <c r="Z17" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA17" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB17" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC17" s="42" t="s">
-        <v>236</v>
+      <c r="D18" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="G18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="M18" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N18" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="O18" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P18" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q18" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="R18" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="S18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="U18" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V18" s="66" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="W18" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="X18" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-EGC-18</v>
+      </c>
+      <c r="Y18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="67" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B17">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B18">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F16">
-    <cfRule type="duplicateValues" dxfId="7" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R17">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="R17:R18">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4950,81 +5324,81 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="L1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="M1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="N1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="Q1" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="U1" s="33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="32">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5088,8 +5462,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="32">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -5156,7 +5530,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5169,38 +5543,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="30">
-        <v>1</v>
-      </c>
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29">
+        <v>1</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="32" t="s">
+      <c r="B2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5211,1122 +5585,2450 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="2.921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AO19"/>
+  <sheetFormatPr defaultColWidth="2.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.15234375" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.15234375" customWidth="1"/>
-    <col min="8" max="8" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="1.921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="1.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.3828125" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.84375" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.84375" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.23046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="9" max="9" width="47.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="4" style="56" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.85546875" customWidth="1"/>
+    <col min="27" max="27" width="3.85546875" style="56" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" style="56" customWidth="1"/>
+    <col min="30" max="30" width="7.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.28515625" style="56" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="L1" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="O1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="P1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="57" t="s">
+      <c r="Q1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="57" t="s">
+      <c r="S1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="T1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="57" t="s">
+      <c r="U1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="V1" s="27" t="s">
+      <c r="V1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="57" t="s">
+      <c r="W1" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="X1" s="29" t="s">
+      <c r="X1" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" s="40" t="s">
+      <c r="Y1" s="26" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="26">
+      <c r="Z1" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB1" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC1" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD1" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE1" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI1" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK1" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM1" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO1" s="39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="78">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="36" t="s">
+      <c r="D2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="M2" s="58">
+      <c r="M2" s="54">
         <v>1.05</v>
       </c>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="O2" s="58">
+      <c r="O2" s="54">
         <v>1.05</v>
       </c>
-      <c r="P2" s="37" t="s">
+      <c r="P2" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="Q2" s="58">
+      <c r="Q2" s="54">
         <v>0</v>
       </c>
-      <c r="R2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26">
+      <c r="R2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="78">
         <v>3</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="36" t="s">
+      <c r="D3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="M3" s="58">
+      <c r="M3" s="54">
         <v>1.05</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="O3" s="58">
+      <c r="O3" s="54">
         <v>1.05</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="P3" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="Q3" s="58">
+      <c r="Q3" s="54">
         <v>0</v>
       </c>
-      <c r="R3" s="37" t="s">
+      <c r="R3" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="S3" s="58">
+      <c r="S3" s="54">
         <v>5.2</v>
       </c>
-      <c r="T3" s="37" t="s">
+      <c r="T3" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="U3" s="58">
+      <c r="U3" s="54">
         <v>0</v>
       </c>
-      <c r="V3" s="37" t="s">
+      <c r="V3" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="54">
         <v>0</v>
       </c>
-      <c r="X3" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26">
+      <c r="X3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="78">
         <v>4</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="36" t="s">
+      <c r="D4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="L4" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="M4" s="58">
+      <c r="M4" s="54">
         <v>2.0499999999999998</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="O4" s="58">
+      <c r="O4" s="54">
         <v>2.0499999999999998</v>
       </c>
-      <c r="P4" s="37" t="s">
+      <c r="P4" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="Q4" s="58">
+      <c r="Q4" s="54">
         <v>0</v>
       </c>
-      <c r="R4" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X4" s="37" t="s">
+      <c r="R4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="Y4" s="47">
+      <c r="Y4" s="37">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26">
+      <c r="Z4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="78">
         <v>5</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="36" t="s">
+      <c r="D5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K5" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="M5" s="58">
+      <c r="M5" s="54">
         <v>3.05</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="O5" s="58">
+      <c r="O5" s="54">
         <v>3.05</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="P5" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="Q5" s="58">
+      <c r="Q5" s="54">
         <v>0</v>
       </c>
-      <c r="R5" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X5" s="37" t="s">
+      <c r="R5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="Y5" s="47">
+      <c r="Y5" s="37">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26">
+      <c r="Z5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="78">
         <v>6</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="36" t="s">
+      <c r="D6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="54">
         <v>4.05</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="54">
         <v>4.05</v>
       </c>
-      <c r="P6" s="37" t="s">
+      <c r="P6" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="54">
         <v>0</v>
       </c>
-      <c r="R6" s="36" t="s">
+      <c r="R6" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="54">
         <v>14.05</v>
       </c>
-      <c r="T6" s="36" t="s">
+      <c r="T6" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="U6" s="58">
+      <c r="U6" s="54">
         <v>14.05</v>
       </c>
-      <c r="V6" s="36" t="s">
+      <c r="V6" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="54">
         <v>0</v>
       </c>
-      <c r="X6" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26">
+      <c r="X6" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="78">
         <v>7</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="36" t="s">
+      <c r="D7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="J7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26">
+      <c r="J7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="78">
         <v>8</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="36" t="s">
+      <c r="D8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26">
+      <c r="J8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="78">
         <v>9</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="50" t="s">
+      <c r="G9" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="J9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="26">
+      <c r="J9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="78">
         <v>10</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="77" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26">
+      <c r="J10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="78">
         <v>11</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="36" t="s">
+      <c r="D11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26">
+      <c r="J11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="78">
         <v>12</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="36" t="s">
+      <c r="D12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="37" t="s">
+      <c r="J12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="Y12" s="47" t="s">
+      <c r="Y12" s="37" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26">
+      <c r="Z12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="78">
         <v>13</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="36" t="s">
+      <c r="D13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="38" t="s">
+      <c r="I13" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="J13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X13" s="37" t="s">
+      <c r="J13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="Y13" s="47">
+      <c r="Y13" s="37">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26">
+      <c r="Z13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="78">
         <v>14</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="36" t="s">
+      <c r="D14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="P14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="U14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="V14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="W14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" s="37" t="s">
+      <c r="J14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="Y14" s="47">
+      <c r="Y14" s="37">
         <v>60</v>
+      </c>
+      <c r="Z14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="78">
+        <v>15</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="70" t="s">
+        <v>248</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA15" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB15" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC15" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD15" s="72" t="str">
+        <f t="shared" ref="AD15:AD19" si="0">IF(AE15="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="AE15" s="73" t="s">
+        <v>249</v>
+      </c>
+      <c r="AF15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="78">
+        <v>16</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="J16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA16" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB16" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC16" s="70" t="s">
+        <v>251</v>
+      </c>
+      <c r="AD16" s="72" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AE16" s="73" t="s">
+        <v>253</v>
+      </c>
+      <c r="AF16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="78">
+        <v>17</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>256</v>
+      </c>
+      <c r="J17" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA17" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB17" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC17" s="70" t="s">
+        <v>255</v>
+      </c>
+      <c r="AD17" s="72" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AE17" s="73" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="78">
+        <v>18</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="70" t="s">
+        <v>260</v>
+      </c>
+      <c r="J18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA18" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB18" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC18" s="70" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD18" s="72" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AE18" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="AF18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="78">
+        <v>19</v>
+      </c>
+      <c r="B19" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="70" t="s">
+        <v>264</v>
+      </c>
+      <c r="J19" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V19" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X19" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA19" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB19" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC19" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="AD19" s="72" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="AE19" s="73" t="s">
+        <v>265</v>
+      </c>
+      <c r="AF19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="75" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B14 H1:I14">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="A1:B2 H1:I14 B3:B14 A3:A19">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:B19">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AO19">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6336,14 +8038,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6351,7 +8053,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6359,7 +8061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6367,7 +8069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6375,7 +8077,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6383,7 +8085,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6391,7 +8093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6399,7 +8101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6407,7 +8109,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6415,7 +8117,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6423,7 +8125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6431,7 +8133,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6439,7 +8141,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6447,7 +8149,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6455,7 +8157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Genetica.xlsx
+++ b/Versão5/PRO/Ontologia_Genetica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA316213-4E78-410D-A613-0F4A542B81A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82F4CF3-8A88-4E0D-B4BB-A48C0CAB988E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -2686,99 +2686,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <b val="0"/>
@@ -3212,15 +3120,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3231,7 +3139,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3242,7 +3150,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3253,7 +3161,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3264,7 +3172,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3276,7 +3184,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3288,7 +3196,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3299,7 +3207,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3310,7 +3218,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3321,7 +3229,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3332,7 +3240,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3343,7 +3251,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3354,7 +3262,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3365,7 +3273,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3376,7 +3284,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3387,7 +3295,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3398,7 +3306,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3409,19 +3317,19 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46259.680473263892</v>
+        <v>46264.568602430554</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="34" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>107</v>
       </c>
@@ -3432,7 +3340,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="34" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -3444,7 +3352,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="34" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -3456,7 +3364,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3467,7 +3375,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3478,7 +3386,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3489,7 +3397,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3500,7 +3408,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>99</v>
       </c>
@@ -3521,36 +3429,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC18"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="10" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3828125" customWidth="1"/>
+    <col min="3" max="3" width="5.53515625" customWidth="1"/>
+    <col min="4" max="4" width="7.53515625" customWidth="1"/>
+    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.15234375" customWidth="1"/>
+    <col min="7" max="10" width="6.3828125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="54.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="62.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.140625" style="56" customWidth="1"/>
-    <col min="21" max="21" width="7.85546875" style="56" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="5.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="54.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.3046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="62.84375" style="56" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.15234375" style="56" customWidth="1"/>
+    <col min="21" max="21" width="7.84375" style="56" customWidth="1"/>
+    <col min="22" max="22" width="11.15234375" style="56" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.3046875" style="56" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.15234375" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.69140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="5.3828125" style="56" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="3" style="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3639,7 +3547,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -3736,7 +3644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -3833,7 +3741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -3930,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -4027,7 +3935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -4124,7 +4032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -4221,7 +4129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -4318,7 +4226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -4415,7 +4323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -4512,7 +4420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -4609,7 +4517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -4706,7 +4614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -4803,7 +4711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -4900,7 +4808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -4997,7 +4905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -5094,7 +5002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -5191,7 +5099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -5202,10 +5110,10 @@
         <v>236</v>
       </c>
       <c r="D18" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="65" t="s">
         <v>237</v>
-      </c>
-      <c r="E18" s="65" t="s">
-        <v>238</v>
       </c>
       <c r="F18" s="65" t="s">
         <v>239</v>
@@ -5231,11 +5139,11 @@
       </c>
       <c r="M18" s="49" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N18" s="49" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O18" s="49" t="str">
         <f t="shared" si="11"/>
@@ -5259,11 +5167,11 @@
       </c>
       <c r="U18" s="41" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V18" s="66" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W18" s="41" t="s">
         <v>90</v>
@@ -5290,26 +5198,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B18">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F16">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17:R18">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5324,15 +5232,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
@@ -5397,7 +5305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5462,7 +5370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="32">
         <v>3</v>
       </c>
@@ -5530,7 +5438,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5543,14 +5451,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -5561,7 +5469,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5574,7 +5482,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5586,52 +5494,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AO19"/>
-  <sheetFormatPr defaultColWidth="2.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" customWidth="1"/>
-    <col min="5" max="5" width="3.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" customWidth="1"/>
-    <col min="9" max="9" width="47.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3046875" customWidth="1"/>
+    <col min="5" max="5" width="3.53515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.69140625" customWidth="1"/>
+    <col min="7" max="7" width="3.3828125" style="56" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.15234375" customWidth="1"/>
+    <col min="9" max="9" width="47.53515625" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="4" style="56" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.85546875" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="56" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.42578125" style="56" customWidth="1"/>
-    <col min="30" max="30" width="7.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.28515625" style="56" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.3828125" style="55" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.84375" style="56" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.84375" style="56" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.84375" style="56" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.3828125" style="55" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.84375" customWidth="1"/>
+    <col min="27" max="27" width="3.84375" style="56" customWidth="1"/>
+    <col min="28" max="28" width="4.84375" style="56" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.3828125" style="56" customWidth="1"/>
+    <col min="30" max="30" width="7.53515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.3046875" style="56" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>91</v>
       </c>
@@ -5756,7 +5664,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="78">
         <v>2</v>
       </c>
@@ -5881,7 +5789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="78">
         <v>3</v>
       </c>
@@ -6006,7 +5914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="78">
         <v>4</v>
       </c>
@@ -6131,7 +6039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="78">
         <v>5</v>
       </c>
@@ -6256,7 +6164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="78">
         <v>6</v>
       </c>
@@ -6381,7 +6289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="78">
         <v>7</v>
       </c>
@@ -6506,7 +6414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="78">
         <v>8</v>
       </c>
@@ -6631,7 +6539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="78">
         <v>9</v>
       </c>
@@ -6756,7 +6664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="78">
         <v>10</v>
       </c>
@@ -6881,7 +6789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="78">
         <v>11</v>
       </c>
@@ -7006,7 +6914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="78">
         <v>12</v>
       </c>
@@ -7131,7 +7039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="78">
         <v>13</v>
       </c>
@@ -7256,7 +7164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="78">
         <v>14</v>
       </c>
@@ -7381,7 +7289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="78">
         <v>15</v>
       </c>
@@ -7507,7 +7415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>16</v>
       </c>
@@ -7633,7 +7541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="78">
         <v>17</v>
       </c>
@@ -7759,7 +7667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="78">
         <v>18</v>
       </c>
@@ -7885,7 +7793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="78">
         <v>19</v>
       </c>
@@ -8013,20 +7921,20 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B2 H1:I14 B3:B14 A3:A19">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+  <conditionalFormatting sqref="A1:B2 B3:B14 H1:I14 A3:A19">
+    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B19">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AO19">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8038,14 +7946,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -8053,7 +7961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -8061,7 +7969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -8069,7 +7977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -8077,7 +7985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -8085,7 +7993,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -8093,7 +8001,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -8101,7 +8009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -8109,7 +8017,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -8117,7 +8025,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -8125,7 +8033,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -8133,7 +8041,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -8141,7 +8049,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -8149,7 +8057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -8157,7 +8065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Genetica.xlsx
+++ b/Versão5/PRO/Ontologia_Genetica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82F4CF3-8A88-4E0D-B4BB-A48C0CAB988E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAAB54B-EED6-48AB-A176-5F4092CA0F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="284">
   <si>
     <t>Key</t>
   </si>
@@ -1981,18 +1981,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2060,6 +2048,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2243,7 +2297,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2400,6 +2454,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2452,7 +2512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2642,9 +2702,6 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2682,11 +2739,17 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -2763,6 +2826,16 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3120,15 +3193,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -3139,7 +3212,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3150,7 +3223,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3161,7 +3234,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3172,7 +3245,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3184,7 +3257,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3196,7 +3269,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3207,7 +3280,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3218,7 +3291,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3229,7 +3302,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3240,7 +3313,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3251,7 +3324,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3262,7 +3335,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3273,7 +3346,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3284,7 +3357,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3295,7 +3368,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3306,7 +3379,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3317,19 +3390,19 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46264.568602430554</v>
+        <v>46268.698638078706</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="34" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>107</v>
       </c>
@@ -3340,7 +3413,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="34" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -3352,7 +3425,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="34" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -3364,7 +3437,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3375,7 +3448,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3386,7 +3459,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3397,7 +3470,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3408,7 +3481,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>99</v>
       </c>
@@ -3428,37 +3501,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC18"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD22"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3828125" customWidth="1"/>
-    <col min="3" max="3" width="5.53515625" customWidth="1"/>
-    <col min="4" max="4" width="7.53515625" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.15234375" customWidth="1"/>
-    <col min="7" max="10" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="54.3828125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.3046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="62.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.15234375" style="56" customWidth="1"/>
-    <col min="21" max="21" width="7.84375" style="56" customWidth="1"/>
-    <col min="22" max="22" width="11.15234375" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.53515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.3046875" style="56" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.15234375" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.69140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="5.3828125" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="76" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="87.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="56" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="56" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="56" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3546,8 +3621,11 @@
       <c r="AC1" s="22" t="s">
         <v>97</v>
       </c>
+      <c r="AD1" s="22" t="s">
+        <v>283</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -3625,26 +3703,29 @@
         <v>90</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X18" si="3">CONCATENATE("Key-EGC-",A2)</f>
+        <f t="shared" ref="X2:X22" si="3">CONCATENATE("Key-EGC-",A2)</f>
         <v>Key-EGC-2</v>
       </c>
-      <c r="Y2" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="67" t="s">
+      <c r="Y2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -3725,23 +3806,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-3</v>
       </c>
-      <c r="Y3" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="67" t="s">
+      <c r="Y3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -3822,23 +3906,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-4</v>
       </c>
-      <c r="Y4" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="67" t="s">
+      <c r="Y4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -3919,23 +4006,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-5</v>
       </c>
-      <c r="Y5" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="67" t="s">
+      <c r="Y5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -4016,23 +4106,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-6</v>
       </c>
-      <c r="Y6" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="67" t="s">
+      <c r="Y6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -4113,23 +4206,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-7</v>
       </c>
-      <c r="Y7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="67" t="s">
+      <c r="Y7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -4210,23 +4306,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-8</v>
       </c>
-      <c r="Y8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="67" t="s">
+      <c r="Y8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -4307,23 +4406,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-9</v>
       </c>
-      <c r="Y9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="67" t="s">
+      <c r="Y9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -4404,23 +4506,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-10</v>
       </c>
-      <c r="Y10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="67" t="s">
+      <c r="Y10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -4501,23 +4606,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-11</v>
       </c>
-      <c r="Y11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="67" t="s">
+      <c r="Y11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -4598,23 +4706,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-12</v>
       </c>
-      <c r="Y12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="67" t="s">
+      <c r="Y12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -4695,23 +4806,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-13</v>
       </c>
-      <c r="Y13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="67" t="s">
+      <c r="Y13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -4792,23 +4906,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-14</v>
       </c>
-      <c r="Y14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="67" t="s">
+      <c r="Y14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -4889,23 +5006,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-15</v>
       </c>
-      <c r="Y15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="67" t="s">
+      <c r="Y15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -4986,23 +5106,26 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-16</v>
       </c>
-      <c r="Y16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="67" t="s">
+      <c r="Y16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -5037,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="49" t="str">
-        <f t="shared" ref="L17:O18" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
+        <f t="shared" ref="L17:O22" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
         <v>Morfológico</v>
       </c>
       <c r="M17" s="49" t="str">
@@ -5065,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="41" t="str">
-        <f t="shared" ref="T17:V18" si="12">SUBSTITUTE(C17, ".", " ")</f>
+        <f t="shared" ref="T17:V22" si="12">SUBSTITUTE(C17, ".", " ")</f>
         <v>Morfológico</v>
       </c>
       <c r="U17" s="41" t="str">
@@ -5083,40 +5206,43 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-17</v>
       </c>
-      <c r="Y17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="67" t="s">
+      <c r="Y17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="57">
         <v>18</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="78" t="s">
         <v>214</v>
       </c>
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="79" t="s">
         <v>236</v>
       </c>
-      <c r="D18" s="65" t="s">
+      <c r="D18" s="79" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="79" t="s">
         <v>237</v>
       </c>
-      <c r="F18" s="65" t="s">
-        <v>239</v>
+      <c r="F18" s="79" t="s">
+        <v>262</v>
       </c>
       <c r="G18" s="62" t="s">
         <v>1</v>
@@ -5147,16 +5273,16 @@
       </c>
       <c r="O18" s="49" t="str">
         <f t="shared" si="11"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P18" s="41" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="Q18" s="41" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="R18" s="41" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="S18" s="41" t="s">
         <v>1</v>
@@ -5169,7 +5295,7 @@
         <f t="shared" si="12"/>
         <v>Macros</v>
       </c>
-      <c r="V18" s="66" t="str">
+      <c r="V18" s="65" t="str">
         <f t="shared" si="12"/>
         <v>Métodos</v>
       </c>
@@ -5180,44 +5306,450 @@
         <f t="shared" si="3"/>
         <v>Key-EGC-18</v>
       </c>
-      <c r="Y18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="67" t="s">
+      <c r="Y18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="57">
+        <v>19</v>
+      </c>
+      <c r="B19" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="D19" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="79" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="M19" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="N19" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O19" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P19" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q19" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="R19" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="S19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="U19" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="V19" s="65" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W19" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="X19" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-EGC-19</v>
+      </c>
+      <c r="Y19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="57">
+        <v>20</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="D20" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="F20" s="79" t="s">
+        <v>270</v>
+      </c>
+      <c r="G20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="M20" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="N20" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O20" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P20" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q20" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="R20" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="S20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="U20" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="V20" s="65" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W20" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="X20" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-EGC-20</v>
+      </c>
+      <c r="Y20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="57">
+        <v>21</v>
+      </c>
+      <c r="B21" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="79" t="s">
+        <v>274</v>
+      </c>
+      <c r="G21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="M21" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="N21" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O21" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P21" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q21" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="R21" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="S21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="U21" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="V21" s="65" t="str">
+        <f t="shared" si="12"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W21" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="X21" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-EGC-21</v>
+      </c>
+      <c r="Y21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="57">
+        <v>22</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="79" t="s">
+        <v>278</v>
+      </c>
+      <c r="F22" s="79" t="s">
+        <v>279</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="M22" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="N22" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O22" s="49" t="str">
+        <f t="shared" si="11"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P22" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q22" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="R22" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="S22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>De API</v>
+      </c>
+      <c r="U22" s="41" t="str">
+        <f t="shared" si="12"/>
+        <v>Macros</v>
+      </c>
+      <c r="V22" s="65" t="str">
+        <f t="shared" si="12"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W22" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="X22" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-EGC-22</v>
+      </c>
+      <c r="Y22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="41" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B18">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B22">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E22:F22">
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F16">
-    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
+  <conditionalFormatting sqref="F18:F21">
     <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R17:R18">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <conditionalFormatting sqref="R17">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5231,16 +5763,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
@@ -5305,7 +5837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5367,71 +5899,6 @@
         <v>1</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5451,14 +5918,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -5469,7 +5936,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5494,52 +5961,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AO19"/>
-  <sheetFormatPr defaultColWidth="2.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="2.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.3046875" customWidth="1"/>
-    <col min="5" max="5" width="3.53515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.69140625" customWidth="1"/>
-    <col min="7" max="7" width="3.3828125" style="56" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.15234375" customWidth="1"/>
-    <col min="9" max="9" width="47.53515625" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="9" max="9" width="47.5703125" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="4" style="56" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.84375" style="55" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.3828125" style="55" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.53515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.53515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.3828125" style="55" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.84375" customWidth="1"/>
-    <col min="27" max="27" width="3.84375" style="56" customWidth="1"/>
-    <col min="28" max="28" width="4.84375" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.3828125" style="56" customWidth="1"/>
-    <col min="30" max="30" width="7.53515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.3046875" style="56" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.85546875" customWidth="1"/>
+    <col min="27" max="27" width="3.85546875" style="56" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" style="56" customWidth="1"/>
+    <col min="30" max="30" width="7.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.28515625" style="56" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>91</v>
       </c>
@@ -5664,8 +6131,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="78">
+    <row r="2" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="77">
         <v>2</v>
       </c>
       <c r="B2" s="27" t="s">
@@ -5677,13 +6144,13 @@
       <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="35" t="s">
@@ -5761,36 +6228,36 @@
       <c r="AF2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG2" s="75" t="s">
+      <c r="AG2" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI2" s="75" t="s">
+      <c r="AI2" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK2" s="75" t="s">
+      <c r="AK2" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM2" s="75" t="s">
+      <c r="AM2" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO2" s="75" t="s">
+      <c r="AO2" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="78">
+    <row r="3" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="77">
         <v>3</v>
       </c>
       <c r="B3" s="27" t="s">
@@ -5802,13 +6269,13 @@
       <c r="D3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="35" t="s">
@@ -5886,36 +6353,36 @@
       <c r="AF3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG3" s="75" t="s">
+      <c r="AG3" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="75" t="s">
+      <c r="AI3" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK3" s="75" t="s">
+      <c r="AK3" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM3" s="75" t="s">
+      <c r="AM3" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO3" s="75" t="s">
+      <c r="AO3" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="78">
+    <row r="4" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="77">
         <v>4</v>
       </c>
       <c r="B4" s="27" t="s">
@@ -5927,13 +6394,13 @@
       <c r="D4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="35" t="s">
@@ -6011,36 +6478,36 @@
       <c r="AF4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG4" s="75" t="s">
+      <c r="AG4" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI4" s="75" t="s">
+      <c r="AI4" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK4" s="75" t="s">
+      <c r="AK4" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM4" s="75" t="s">
+      <c r="AM4" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO4" s="75" t="s">
+      <c r="AO4" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="78">
+    <row r="5" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="77">
         <v>5</v>
       </c>
       <c r="B5" s="27" t="s">
@@ -6052,13 +6519,13 @@
       <c r="D5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H5" s="35" t="s">
@@ -6136,36 +6603,36 @@
       <c r="AF5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG5" s="75" t="s">
+      <c r="AG5" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI5" s="75" t="s">
+      <c r="AI5" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK5" s="75" t="s">
+      <c r="AK5" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM5" s="75" t="s">
+      <c r="AM5" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO5" s="75" t="s">
+      <c r="AO5" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="78">
+    <row r="6" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="77">
         <v>6</v>
       </c>
       <c r="B6" s="27" t="s">
@@ -6177,13 +6644,13 @@
       <c r="D6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="76" t="s">
+      <c r="E6" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="76" t="s">
+      <c r="G6" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="35" t="s">
@@ -6261,36 +6728,36 @@
       <c r="AF6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG6" s="75" t="s">
+      <c r="AG6" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI6" s="75" t="s">
+      <c r="AI6" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK6" s="75" t="s">
+      <c r="AK6" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM6" s="75" t="s">
+      <c r="AM6" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN6" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO6" s="75" t="s">
+      <c r="AO6" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="78">
+    <row r="7" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="77">
         <v>7</v>
       </c>
       <c r="B7" s="27" t="s">
@@ -6302,13 +6769,13 @@
       <c r="D7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="76" t="s">
+      <c r="G7" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H7" s="35" t="s">
@@ -6386,36 +6853,36 @@
       <c r="AF7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG7" s="75" t="s">
+      <c r="AG7" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI7" s="75" t="s">
+      <c r="AI7" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK7" s="75" t="s">
+      <c r="AK7" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM7" s="75" t="s">
+      <c r="AM7" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN7" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO7" s="75" t="s">
+      <c r="AO7" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="78">
+    <row r="8" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="77">
         <v>8</v>
       </c>
       <c r="B8" s="27" t="s">
@@ -6427,13 +6894,13 @@
       <c r="D8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="76" t="s">
+      <c r="E8" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="76" t="s">
+      <c r="G8" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H8" s="35" t="s">
@@ -6511,36 +6978,36 @@
       <c r="AF8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG8" s="75" t="s">
+      <c r="AG8" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI8" s="75" t="s">
+      <c r="AI8" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK8" s="75" t="s">
+      <c r="AK8" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM8" s="75" t="s">
+      <c r="AM8" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN8" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO8" s="75" t="s">
+      <c r="AO8" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="78">
+    <row r="9" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="77">
         <v>9</v>
       </c>
       <c r="B9" s="27" t="s">
@@ -6552,13 +7019,13 @@
       <c r="D9" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="76" t="s">
         <v>130</v>
       </c>
       <c r="F9" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="76" t="s">
         <v>133</v>
       </c>
       <c r="H9" s="35" t="s">
@@ -6636,36 +7103,36 @@
       <c r="AF9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG9" s="75" t="s">
+      <c r="AG9" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI9" s="75" t="s">
+      <c r="AI9" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK9" s="75" t="s">
+      <c r="AK9" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM9" s="75" t="s">
+      <c r="AM9" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO9" s="75" t="s">
+      <c r="AO9" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="78">
+    <row r="10" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="77">
         <v>10</v>
       </c>
       <c r="B10" s="27" t="s">
@@ -6677,13 +7144,13 @@
       <c r="D10" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="76" t="s">
         <v>130</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="76" t="s">
         <v>188</v>
       </c>
       <c r="H10" s="35" t="s">
@@ -6761,36 +7228,36 @@
       <c r="AF10" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG10" s="75" t="s">
+      <c r="AG10" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH10" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI10" s="75" t="s">
+      <c r="AI10" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ10" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK10" s="75" t="s">
+      <c r="AK10" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL10" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM10" s="75" t="s">
+      <c r="AM10" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN10" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO10" s="75" t="s">
+      <c r="AO10" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="78">
+    <row r="11" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="77">
         <v>11</v>
       </c>
       <c r="B11" s="27" t="s">
@@ -6802,13 +7269,13 @@
       <c r="D11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="76" t="s">
+      <c r="G11" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H11" s="35" t="s">
@@ -6886,36 +7353,36 @@
       <c r="AF11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG11" s="75" t="s">
+      <c r="AG11" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI11" s="75" t="s">
+      <c r="AI11" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK11" s="75" t="s">
+      <c r="AK11" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM11" s="75" t="s">
+      <c r="AM11" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO11" s="75" t="s">
+      <c r="AO11" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="78">
+    <row r="12" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="77">
         <v>12</v>
       </c>
       <c r="B12" s="27" t="s">
@@ -6927,13 +7394,13 @@
       <c r="D12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="76" t="s">
+      <c r="G12" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="35" t="s">
@@ -7011,36 +7478,36 @@
       <c r="AF12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG12" s="75" t="s">
+      <c r="AG12" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI12" s="75" t="s">
+      <c r="AI12" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK12" s="75" t="s">
+      <c r="AK12" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM12" s="75" t="s">
+      <c r="AM12" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN12" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO12" s="75" t="s">
+      <c r="AO12" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="78">
+    <row r="13" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="77">
         <v>13</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -7052,13 +7519,13 @@
       <c r="D13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="76" t="s">
+      <c r="G13" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="35" t="s">
@@ -7136,36 +7603,36 @@
       <c r="AF13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG13" s="75" t="s">
+      <c r="AG13" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI13" s="75" t="s">
+      <c r="AI13" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK13" s="75" t="s">
+      <c r="AK13" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM13" s="75" t="s">
+      <c r="AM13" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN13" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO13" s="75" t="s">
+      <c r="AO13" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="78">
+    <row r="14" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="77">
         <v>14</v>
       </c>
       <c r="B14" s="27" t="s">
@@ -7177,13 +7644,13 @@
       <c r="D14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="G14" s="75" t="s">
         <v>1</v>
       </c>
       <c r="H14" s="35" t="s">
@@ -7261,187 +7728,187 @@
       <c r="AF14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG14" s="75" t="s">
+      <c r="AG14" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI14" s="75" t="s">
+      <c r="AI14" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK14" s="75" t="s">
+      <c r="AK14" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM14" s="75" t="s">
+      <c r="AM14" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN14" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO14" s="75" t="s">
+      <c r="AO14" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="78">
+    <row r="15" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="77">
         <v>15</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="79" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="U15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA15" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB15" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC15" s="69" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="70" t="s">
-        <v>248</v>
-      </c>
-      <c r="J15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="AA15" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB15" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC15" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="AD15" s="72" t="str">
+      <c r="AD15" s="71" t="str">
         <f t="shared" ref="AD15:AD19" si="0">IF(AE15="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="AE15" s="73" t="s">
-        <v>249</v>
+      <c r="AE15" s="72" t="s">
+        <v>245</v>
       </c>
       <c r="AF15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG15" s="75" t="s">
+      <c r="AG15" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI15" s="75" t="s">
+      <c r="AI15" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK15" s="75" t="s">
+      <c r="AK15" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM15" s="75" t="s">
+      <c r="AM15" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN15" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO15" s="75" t="s">
+      <c r="AO15" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="78">
+    <row r="16" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="77">
         <v>16</v>
       </c>
-      <c r="B16" s="68" t="s">
-        <v>250</v>
-      </c>
-      <c r="C16" s="65" t="s">
-        <v>239</v>
+      <c r="B16" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="79" t="s">
+        <v>274</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E16" s="76" t="s">
+      <c r="E16" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="71" t="s">
+      <c r="G16" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="70" t="s">
-        <v>252</v>
+      <c r="I16" s="69" t="s">
+        <v>248</v>
       </c>
       <c r="J16" s="36" t="s">
         <v>1</v>
@@ -7491,83 +7958,83 @@
       <c r="Y16" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Z16" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="AA16" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB16" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC16" s="70" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD16" s="72" t="str">
+      <c r="Z16" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA16" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB16" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC16" s="69" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD16" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE16" s="73" t="s">
-        <v>253</v>
+      <c r="AE16" s="72" t="s">
+        <v>249</v>
       </c>
       <c r="AF16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG16" s="75" t="s">
+      <c r="AG16" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI16" s="75" t="s">
+      <c r="AI16" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK16" s="75" t="s">
+      <c r="AK16" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM16" s="75" t="s">
+      <c r="AM16" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN16" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO16" s="75" t="s">
+      <c r="AO16" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78">
+    <row r="17" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="77">
         <v>17</v>
       </c>
-      <c r="B17" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="C17" s="65" t="s">
-        <v>239</v>
+      <c r="B17" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="79" t="s">
+        <v>274</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="71" t="s">
+      <c r="G17" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="70" t="s">
-        <v>256</v>
+      <c r="I17" s="69" t="s">
+        <v>252</v>
       </c>
       <c r="J17" s="36" t="s">
         <v>1</v>
@@ -7617,83 +8084,83 @@
       <c r="Y17" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Z17" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="AA17" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB17" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC17" s="70" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD17" s="72" t="str">
+      <c r="Z17" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA17" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB17" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC17" s="69" t="s">
+        <v>251</v>
+      </c>
+      <c r="AD17" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE17" s="73" t="s">
-        <v>257</v>
+      <c r="AE17" s="72" t="s">
+        <v>253</v>
       </c>
       <c r="AF17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG17" s="75" t="s">
+      <c r="AG17" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI17" s="75" t="s">
+      <c r="AI17" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK17" s="75" t="s">
+      <c r="AK17" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM17" s="75" t="s">
+      <c r="AM17" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN17" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO17" s="75" t="s">
+      <c r="AO17" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="78">
+    <row r="18" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="77">
         <v>18</v>
       </c>
-      <c r="B18" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="C18" s="65" t="s">
-        <v>239</v>
+      <c r="B18" s="67" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="79" t="s">
+        <v>274</v>
       </c>
       <c r="D18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="71" t="s">
+      <c r="G18" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="70" t="s">
-        <v>260</v>
+      <c r="I18" s="69" t="s">
+        <v>256</v>
       </c>
       <c r="J18" s="36" t="s">
         <v>1</v>
@@ -7743,83 +8210,83 @@
       <c r="Y18" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Z18" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="AA18" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB18" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC18" s="70" t="s">
-        <v>259</v>
-      </c>
-      <c r="AD18" s="72" t="str">
+      <c r="Z18" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA18" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB18" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC18" s="69" t="s">
+        <v>255</v>
+      </c>
+      <c r="AD18" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE18" s="73" t="s">
-        <v>261</v>
+      <c r="AE18" s="72" t="s">
+        <v>257</v>
       </c>
       <c r="AF18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG18" s="75" t="s">
+      <c r="AG18" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI18" s="75" t="s">
+      <c r="AI18" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK18" s="75" t="s">
+      <c r="AK18" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM18" s="75" t="s">
+      <c r="AM18" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN18" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO18" s="75" t="s">
+      <c r="AO18" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:41" s="74" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="78">
+    <row r="19" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="77">
         <v>19</v>
       </c>
-      <c r="B19" s="68" t="s">
-        <v>262</v>
-      </c>
-      <c r="C19" s="65" t="s">
-        <v>239</v>
+      <c r="B19" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" s="79" t="s">
+        <v>274</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="75" t="s">
         <v>1</v>
       </c>
       <c r="F19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G19" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="71" t="s">
+      <c r="G19" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="70" t="s">
-        <v>264</v>
+      <c r="I19" s="69" t="s">
+        <v>260</v>
       </c>
       <c r="J19" s="36" t="s">
         <v>1</v>
@@ -7869,72 +8336,72 @@
       <c r="Y19" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Z19" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="AA19" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB19" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC19" s="70" t="s">
-        <v>263</v>
-      </c>
-      <c r="AD19" s="72" t="str">
+      <c r="Z19" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA19" s="69" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB19" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC19" s="69" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD19" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE19" s="73" t="s">
-        <v>265</v>
+      <c r="AE19" s="72" t="s">
+        <v>261</v>
       </c>
       <c r="AF19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AG19" s="75" t="s">
+      <c r="AG19" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AH19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AI19" s="75" t="s">
+      <c r="AI19" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AJ19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AK19" s="75" t="s">
+      <c r="AK19" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AL19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AM19" s="75" t="s">
+      <c r="AM19" s="74" t="s">
         <v>1</v>
       </c>
       <c r="AN19" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="AO19" s="75" t="s">
+      <c r="AO19" s="74" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B2 B3:B14 H1:I14 A3:A19">
-    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B19">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AO19">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7946,14 +8413,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -7961,7 +8428,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -7969,7 +8436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -7977,7 +8444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -7985,7 +8452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -7993,7 +8460,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -8001,7 +8468,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -8009,7 +8476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -8017,7 +8484,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -8025,7 +8492,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -8033,7 +8500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -8041,7 +8508,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -8049,7 +8516,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -8057,7 +8524,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -8065,7 +8532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Genetica.xlsx
+++ b/Versão5/PRO/Ontologia_Genetica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAAB54B-EED6-48AB-A176-5F4092CA0F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4B0013-E011-45F0-A671-E7BA1A893432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="286">
   <si>
     <t>Key</t>
   </si>
@@ -1972,15 +1972,6 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2098,9 +2089,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -2114,6 +2102,24 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
   </si>
 </sst>
 </file>
@@ -2512,7 +2518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2578,12 +2584,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2657,9 +2657,6 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2688,9 +2685,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2739,17 +2733,82 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2866,14 +2925,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3197,7 +3248,7 @@
   <cols>
     <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
     <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
@@ -3208,7 +3259,7 @@
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="36" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3219,7 +3270,7 @@
       <c r="B2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3230,7 +3281,7 @@
       <c r="B3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3241,7 +3292,7 @@
       <c r="B4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3253,7 +3304,7 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3265,7 +3316,7 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3276,7 +3327,7 @@
       <c r="B7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3287,7 +3338,7 @@
       <c r="B8" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3298,7 +3349,7 @@
       <c r="B9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3309,7 +3360,7 @@
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3320,7 +3371,7 @@
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3331,7 +3382,7 @@
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3342,7 +3393,7 @@
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3353,7 +3404,7 @@
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3364,7 +3415,7 @@
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3375,7 +3426,7 @@
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3386,7 +3437,7 @@
       <c r="B17" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3396,44 +3447,44 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46268.698638078706</v>
-      </c>
-      <c r="C18" s="42" t="s">
+        <v>46274.378820370373</v>
+      </c>
+      <c r="C18" s="40" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="32" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="40" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="32" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="44" t="str">
+      <c r="B20" s="42" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="40" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="34" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="32" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="44" t="str">
+      <c r="B21" s="42" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="40" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3444,7 +3495,7 @@
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3455,7 +3506,7 @@
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3466,7 +3517,7 @@
       <c r="B24" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="40" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3477,7 +3528,7 @@
       <c r="B25" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="40" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3489,7 +3540,7 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="40" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3505,31 +3556,31 @@
   <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="10" width="7.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.28515625" customWidth="1"/>
     <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="76" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="88.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="87.42578125" style="56" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="56" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.42578125" style="56" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.42578125" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="57" customWidth="1"/>
+    <col min="17" max="17" width="66.5703125" customWidth="1"/>
+    <col min="18" max="18" width="64.85546875" style="53" customWidth="1"/>
+    <col min="19" max="19" width="4.42578125" style="82" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" style="53" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" style="53" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" style="53" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" style="53" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.140625" style="53" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="3.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3552,19 +3603,19 @@
       <c r="F1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="48" t="s">
         <v>43</v>
       </c>
       <c r="L1" s="22" t="s">
@@ -3585,10 +3636,10 @@
       <c r="Q1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="81" t="s">
         <v>88</v>
       </c>
       <c r="T1" s="22" t="s">
@@ -3603,7 +3654,7 @@
       <c r="W1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="59" t="s">
+      <c r="X1" s="56" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="22" t="s">
@@ -3622,2136 +3673,2134 @@
         <v>97</v>
       </c>
       <c r="AD1" s="22" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57">
+      <c r="A2" s="54">
         <v>2</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="79" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="48" t="str">
+      <c r="G2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="46" t="str">
         <f t="shared" ref="L2:L16" si="0">_xlfn.CONCAT(C2)</f>
         <v>Formantes</v>
       </c>
-      <c r="M2" s="48" t="str">
+      <c r="M2" s="46" t="str">
         <f t="shared" ref="M2:O16" si="1">_xlfn.CONCAT("", D2)</f>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N2" s="48" t="str">
+      <c r="N2" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O2" s="48" t="str">
+      <c r="O2" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Valor.X</v>
       </c>
-      <c r="P2" s="48" t="s">
+      <c r="P2" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="Q2" s="48" t="s">
+      <c r="Q2" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="R2" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="S2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="41" t="str">
+      <c r="S2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="39" t="str">
         <f t="shared" ref="T2:V16" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="U2" s="41" t="str">
+      <c r="U2" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V2" s="49" t="str">
+      <c r="V2" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W2" s="41" t="s">
+      <c r="W2" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X2" s="58" t="str">
+      <c r="X2" s="55" t="str">
         <f t="shared" ref="X2:X22" si="3">CONCATENATE("Key-EGC-",A2)</f>
         <v>Key-EGC-2</v>
       </c>
-      <c r="Y2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="66" t="s">
+      <c r="Y2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57">
+      <c r="A3" s="54">
         <v>3</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="48" t="str">
+      <c r="G3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M3" s="48" t="str">
+      <c r="M3" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N3" s="48" t="str">
+      <c r="N3" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O3" s="48" t="str">
+      <c r="O3" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Y</v>
       </c>
-      <c r="P3" s="48" t="s">
+      <c r="P3" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="Q3" s="48" t="s">
+      <c r="Q3" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="R3" s="41" t="s">
+      <c r="R3" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="41" t="str">
+      <c r="S3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U3" s="41" t="str">
+      <c r="U3" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V3" s="49" t="str">
+      <c r="V3" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W3" s="41" t="s">
+      <c r="W3" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X3" s="58" t="str">
+      <c r="X3" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-3</v>
       </c>
-      <c r="Y3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="66" t="s">
+      <c r="Y3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57">
+      <c r="A4" s="54">
         <v>4</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="79" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="48" t="str">
+      <c r="G4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M4" s="48" t="str">
+      <c r="M4" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N4" s="48" t="str">
+      <c r="N4" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O4" s="48" t="str">
+      <c r="O4" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Z</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="R4" s="41" t="s">
+      <c r="R4" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="S4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="41" t="str">
+      <c r="S4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U4" s="41" t="str">
+      <c r="U4" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V4" s="49" t="str">
+      <c r="V4" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W4" s="41" t="s">
+      <c r="W4" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X4" s="58" t="str">
+      <c r="X4" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-4</v>
       </c>
-      <c r="Y4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="66" t="s">
+      <c r="Y4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57">
+      <c r="A5" s="54">
         <v>5</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="79" t="s">
         <v>171</v>
       </c>
-      <c r="G5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="48" t="str">
+      <c r="G5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M5" s="48" t="str">
+      <c r="M5" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N5" s="48" t="str">
+      <c r="N5" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O5" s="48" t="str">
+      <c r="O5" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Distância</v>
       </c>
-      <c r="P5" s="48" t="s">
+      <c r="P5" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="Q5" s="48" t="s">
+      <c r="Q5" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="R5" s="41" t="s">
+      <c r="R5" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="S5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="41" t="str">
+      <c r="S5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U5" s="41" t="str">
+      <c r="U5" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V5" s="49" t="str">
+      <c r="V5" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W5" s="41" t="s">
+      <c r="W5" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X5" s="58" t="str">
+      <c r="X5" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-5</v>
       </c>
-      <c r="Y5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="66" t="s">
+      <c r="Y5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57">
+      <c r="A6" s="54">
         <v>6</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="G6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="48" t="str">
+      <c r="G6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M6" s="48" t="str">
+      <c r="M6" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N6" s="48" t="str">
+      <c r="N6" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O6" s="48" t="str">
+      <c r="O6" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Angular</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="Q6" s="48" t="s">
+      <c r="Q6" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="R6" s="41" t="s">
+      <c r="R6" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="S6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="41" t="str">
+      <c r="S6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U6" s="41" t="str">
+      <c r="U6" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V6" s="49" t="str">
+      <c r="V6" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W6" s="41" t="s">
+      <c r="W6" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X6" s="58" t="str">
+      <c r="X6" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-6</v>
       </c>
-      <c r="Y6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="66" t="s">
+      <c r="Y6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57">
+      <c r="A7" s="54">
         <v>7</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="48" t="str">
+      <c r="G7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M7" s="48" t="str">
+      <c r="M7" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N7" s="48" t="str">
+      <c r="N7" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="O7" s="48" t="str">
+      <c r="O7" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Valor.Escalar</v>
       </c>
-      <c r="P7" s="48" t="s">
+      <c r="P7" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="Q7" s="48" t="s">
+      <c r="Q7" s="46" t="s">
         <v>228</v>
       </c>
-      <c r="R7" s="41" t="s">
+      <c r="R7" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="S7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="41" t="str">
+      <c r="S7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U7" s="41" t="str">
+      <c r="U7" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V7" s="49" t="str">
+      <c r="V7" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Parâmetros</v>
       </c>
-      <c r="W7" s="41" t="s">
+      <c r="W7" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X7" s="58" t="str">
+      <c r="X7" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-7</v>
       </c>
-      <c r="Y7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="66" t="s">
+      <c r="Y7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57">
+      <c r="A8" s="54">
         <v>8</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="79" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="48" t="str">
+      <c r="G8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M8" s="48" t="str">
+      <c r="M8" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N8" s="48" t="str">
+      <c r="N8" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O8" s="48" t="str">
+      <c r="O8" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Eixo1</v>
       </c>
-      <c r="P8" s="48" t="s">
+      <c r="P8" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="Q8" s="48" t="s">
+      <c r="Q8" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="R8" s="41" t="s">
+      <c r="R8" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="S8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="41" t="str">
+      <c r="S8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U8" s="41" t="str">
+      <c r="U8" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V8" s="49" t="str">
+      <c r="V8" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W8" s="41" t="s">
+      <c r="W8" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X8" s="58" t="str">
+      <c r="X8" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-8</v>
       </c>
-      <c r="Y8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="66" t="s">
+      <c r="Y8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57">
+      <c r="A9" s="54">
         <v>9</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="48" t="str">
+      <c r="G9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M9" s="48" t="str">
+      <c r="M9" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N9" s="48" t="str">
+      <c r="N9" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O9" s="48" t="str">
+      <c r="O9" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Eixo2</v>
       </c>
-      <c r="P9" s="48" t="s">
+      <c r="P9" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="Q9" s="48" t="s">
+      <c r="Q9" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="R9" s="41" t="s">
+      <c r="R9" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="S9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="41" t="str">
+      <c r="S9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U9" s="41" t="str">
+      <c r="U9" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V9" s="49" t="str">
+      <c r="V9" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W9" s="41" t="s">
+      <c r="W9" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X9" s="58" t="str">
+      <c r="X9" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-9</v>
       </c>
-      <c r="Y9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="66" t="s">
+      <c r="Y9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="57">
+      <c r="A10" s="54">
         <v>10</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="48" t="str">
+      <c r="G10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M10" s="48" t="str">
+      <c r="M10" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N10" s="48" t="str">
+      <c r="N10" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O10" s="48" t="str">
+      <c r="O10" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Base</v>
       </c>
-      <c r="P10" s="48" t="s">
+      <c r="P10" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="Q10" s="48" t="s">
+      <c r="Q10" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="R10" s="41" t="s">
+      <c r="R10" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="S10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="41" t="str">
+      <c r="S10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U10" s="41" t="str">
+      <c r="U10" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V10" s="49" t="str">
+      <c r="V10" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W10" s="41" t="s">
+      <c r="W10" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X10" s="58" t="str">
+      <c r="X10" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-10</v>
       </c>
-      <c r="Y10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="66" t="s">
+      <c r="Y10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="57">
+      <c r="A11" s="54">
         <v>11</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="F11" s="45" t="s">
+      <c r="F11" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="48" t="str">
+      <c r="G11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M11" s="48" t="str">
+      <c r="M11" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N11" s="48" t="str">
+      <c r="N11" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="O11" s="48" t="str">
+      <c r="O11" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Ponto.Destino</v>
       </c>
-      <c r="P11" s="48" t="s">
+      <c r="P11" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="Q11" s="48" t="s">
+      <c r="Q11" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="R11" s="41" t="s">
+      <c r="R11" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="S11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="41" t="str">
+      <c r="S11" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U11" s="41" t="str">
+      <c r="U11" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V11" s="49" t="str">
+      <c r="V11" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Bases</v>
       </c>
-      <c r="W11" s="41" t="s">
+      <c r="W11" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X11" s="58" t="str">
+      <c r="X11" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-11</v>
       </c>
-      <c r="Y11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="66" t="s">
+      <c r="Y11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57">
+      <c r="A12" s="54">
         <v>12</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="78" t="s">
         <v>222</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="79" t="s">
         <v>172</v>
       </c>
-      <c r="G12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="52" t="s">
+      <c r="G12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="L12" s="48" t="str">
+      <c r="L12" s="46" t="str">
         <f t="shared" ref="L12" si="4">_xlfn.CONCAT(C12)</f>
         <v>Formantes</v>
       </c>
-      <c r="M12" s="48" t="str">
+      <c r="M12" s="46" t="str">
         <f t="shared" ref="M12" si="5">_xlfn.CONCAT("", D12)</f>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N12" s="48" t="str">
+      <c r="N12" s="46" t="str">
         <f t="shared" ref="N12" si="6">_xlfn.CONCAT("", E12)</f>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O12" s="48" t="str">
+      <c r="O12" s="46" t="str">
         <f t="shared" ref="O12" si="7">_xlfn.CONCAT("", F12)</f>
         <v>Translação.XYZ</v>
       </c>
-      <c r="P12" s="48" t="s">
+      <c r="P12" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="Q12" s="48" t="s">
+      <c r="Q12" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="R12" s="41" t="s">
+      <c r="R12" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="S12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="41" t="str">
+      <c r="S12" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="39" t="str">
         <f t="shared" ref="T12" si="8">SUBSTITUTE(C12, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="U12" s="41" t="str">
+      <c r="U12" s="39" t="str">
         <f t="shared" ref="U12" si="9">SUBSTITUTE(D12, "_", " ")</f>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V12" s="49" t="str">
+      <c r="V12" s="47" t="str">
         <f t="shared" ref="V12" si="10">SUBSTITUTE(E12, "_", " ")</f>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W12" s="41" t="s">
+      <c r="W12" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X12" s="58" t="str">
+      <c r="X12" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-12</v>
       </c>
-      <c r="Y12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="66" t="s">
+      <c r="Y12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="57">
+      <c r="A13" s="54">
         <v>13</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="78" t="s">
         <v>222</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="52" t="s">
+      <c r="G13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="L13" s="48" t="str">
+      <c r="L13" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M13" s="48" t="str">
+      <c r="M13" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N13" s="48" t="str">
+      <c r="N13" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O13" s="48" t="str">
+      <c r="O13" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Translação.Polar</v>
       </c>
-      <c r="P13" s="48" t="s">
+      <c r="P13" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="Q13" s="48" t="s">
+      <c r="Q13" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="R13" s="41" t="s">
+      <c r="R13" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="S13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="41" t="str">
+      <c r="S13" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U13" s="41" t="str">
+      <c r="U13" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V13" s="49" t="str">
+      <c r="V13" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W13" s="41" t="s">
+      <c r="W13" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X13" s="58" t="str">
+      <c r="X13" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-13</v>
       </c>
-      <c r="Y13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="66" t="s">
+      <c r="Y13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57">
+      <c r="A14" s="54">
         <v>14</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="78" t="s">
         <v>222</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="52" t="s">
+      <c r="G14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="L14" s="48" t="str">
+      <c r="L14" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M14" s="48" t="str">
+      <c r="M14" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N14" s="48" t="str">
+      <c r="N14" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O14" s="48" t="str">
+      <c r="O14" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Giro</v>
       </c>
-      <c r="P14" s="48" t="s">
+      <c r="P14" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="Q14" s="48" t="s">
+      <c r="Q14" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="R14" s="41" t="s">
+      <c r="R14" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="S14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="41" t="str">
+      <c r="S14" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U14" s="41" t="str">
+      <c r="U14" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V14" s="49" t="str">
+      <c r="V14" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W14" s="41" t="s">
+      <c r="W14" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X14" s="58" t="str">
+      <c r="X14" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-14</v>
       </c>
-      <c r="Y14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="66" t="s">
+      <c r="Y14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57">
+      <c r="A15" s="54">
         <v>15</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="78" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="52" t="s">
+      <c r="G15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="49" t="s">
         <v>209</v>
       </c>
-      <c r="L15" s="48" t="str">
+      <c r="L15" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M15" s="48" t="str">
+      <c r="M15" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N15" s="48" t="str">
+      <c r="N15" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O15" s="48" t="str">
+      <c r="O15" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Escalar</v>
       </c>
-      <c r="P15" s="48" t="s">
+      <c r="P15" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="Q15" s="48" t="s">
+      <c r="Q15" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="R15" s="41" t="s">
+      <c r="R15" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="S15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="41" t="str">
+      <c r="S15" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U15" s="41" t="str">
+      <c r="U15" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V15" s="49" t="str">
+      <c r="V15" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W15" s="41" t="s">
+      <c r="W15" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X15" s="58" t="str">
+      <c r="X15" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-15</v>
       </c>
-      <c r="Y15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="66" t="s">
+      <c r="Y15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="57">
+      <c r="A16" s="54">
         <v>16</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="78" t="s">
         <v>222</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="52" t="s">
+      <c r="G16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="L16" s="48" t="str">
+      <c r="L16" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
-      <c r="M16" s="48" t="str">
+      <c r="M16" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="N16" s="48" t="str">
+      <c r="N16" s="46" t="str">
         <f t="shared" si="1"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="O16" s="48" t="str">
+      <c r="O16" s="46" t="str">
         <f t="shared" si="1"/>
         <v>Reflexão</v>
       </c>
-      <c r="P16" s="48" t="s">
+      <c r="P16" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="Q16" s="48" t="s">
+      <c r="Q16" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="R16" s="41" t="s">
+      <c r="R16" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="S16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="41" t="str">
+      <c r="S16" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Formantes</v>
       </c>
-      <c r="U16" s="41" t="str">
+      <c r="U16" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Elementos.EGC</v>
       </c>
-      <c r="V16" s="49" t="str">
+      <c r="V16" s="47" t="str">
         <f t="shared" si="2"/>
         <v>EGC.Movimentos</v>
       </c>
-      <c r="W16" s="41" t="s">
+      <c r="W16" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X16" s="58" t="str">
+      <c r="X16" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-16</v>
       </c>
-      <c r="Y16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="66" t="s">
+      <c r="Y16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="57">
+    <row r="17" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="54">
         <v>17</v>
       </c>
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="80" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="80" t="s">
         <v>218</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="80" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="F17" s="80" t="s">
         <v>216</v>
       </c>
-      <c r="G17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="49" t="str">
+      <c r="G17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="47" t="str">
         <f t="shared" ref="L17:O22" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
         <v>Morfológico</v>
       </c>
-      <c r="M17" s="49" t="str">
+      <c r="M17" s="47" t="str">
         <f t="shared" si="11"/>
         <v>Morfologias</v>
       </c>
-      <c r="N17" s="49" t="str">
+      <c r="N17" s="47" t="str">
         <f t="shared" si="11"/>
         <v>Códificação Formal</v>
       </c>
-      <c r="O17" s="49" t="str">
+      <c r="O17" s="47" t="str">
         <f t="shared" si="11"/>
         <v>Código De Forma</v>
       </c>
-      <c r="P17" s="41" t="s">
+      <c r="P17" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="Q17" s="63" t="s">
+      <c r="Q17" s="59" t="s">
         <v>232</v>
       </c>
-      <c r="R17" s="41" t="s">
+      <c r="R17" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="S17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="41" t="str">
+      <c r="S17" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="39" t="str">
         <f t="shared" ref="T17:V22" si="12">SUBSTITUTE(C17, ".", " ")</f>
         <v>Morfológico</v>
       </c>
-      <c r="U17" s="41" t="str">
+      <c r="U17" s="39" t="str">
         <f t="shared" si="12"/>
         <v>Morfologias</v>
       </c>
-      <c r="V17" s="41" t="str">
+      <c r="V17" s="39" t="str">
         <f t="shared" si="12"/>
         <v>Códificação Formal</v>
       </c>
-      <c r="W17" s="41" t="s">
+      <c r="W17" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X17" s="58" t="str">
+      <c r="X17" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-EGC-17</v>
       </c>
-      <c r="Y17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="66" t="s">
+      <c r="Y17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="57">
+    <row r="18" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="54">
         <v>18</v>
       </c>
-      <c r="B18" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D18" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="F18" s="79" t="s">
+      <c r="B18" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="E18" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>259</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="47" t="str">
+        <f t="shared" ref="L18:M22" si="13">CONCATENATE("", C18)</f>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M18" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N18" s="47" t="str">
+        <f t="shared" ref="N18:O22" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
+        <v>API Método</v>
+      </c>
+      <c r="O18" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P18" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q18" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="R18" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="G18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="M18" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="N18" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O18" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P18" s="41" t="s">
+      <c r="S18" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="39" t="str">
+        <f t="shared" si="12"/>
+        <v>API Plataforma</v>
+      </c>
+      <c r="U18" s="39" t="str">
+        <f t="shared" si="12"/>
+        <v>API Macros</v>
+      </c>
+      <c r="V18" s="61" t="str">
+        <f t="shared" si="12"/>
+        <v>API Método</v>
+      </c>
+      <c r="W18" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="X18" s="55" t="str">
+        <f t="shared" ref="X18:X22" si="15">CONCATENATE("Key-EGC-",A18)</f>
+        <v>Key-EGC-18</v>
+      </c>
+      <c r="Y18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="54">
+        <v>19</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="E19" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F19" s="80" t="s">
         <v>263</v>
       </c>
-      <c r="Q18" s="41" t="s">
+      <c r="G19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M19" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N19" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>API Método</v>
+      </c>
+      <c r="O19" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P19" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="R18" s="41" t="s">
+      <c r="Q19" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="S18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="41" t="str">
+      <c r="R19" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="S19" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="U18" s="41" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U19" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="V18" s="65" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V19" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W18" s="41" t="s">
+        <v>API Método</v>
+      </c>
+      <c r="W19" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X18" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-EGC-18</v>
-      </c>
-      <c r="Y18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="41" t="s">
+      <c r="X19" s="55" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-EGC-19</v>
+      </c>
+      <c r="Y19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="57">
-        <v>19</v>
-      </c>
-      <c r="B19" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="C19" s="79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D19" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="E19" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="79" t="s">
-        <v>266</v>
-      </c>
-      <c r="G19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="M19" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="N19" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O19" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P19" s="41" t="s">
+    <row r="20" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="54">
+        <v>20</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="E20" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F20" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="Q19" s="41" t="s">
+      <c r="G20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M20" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N20" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>API Método</v>
+      </c>
+      <c r="O20" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P20" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="R19" s="41" t="s">
+      <c r="Q20" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="S19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="41" t="str">
+      <c r="R20" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="S20" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="U19" s="41" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U20" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="V19" s="65" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V20" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W19" s="41" t="s">
+        <v>API Método</v>
+      </c>
+      <c r="W20" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X19" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-EGC-19</v>
-      </c>
-      <c r="Y19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="41" t="s">
+      <c r="X20" s="55" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-EGC-20</v>
+      </c>
+      <c r="Y20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="57">
-        <v>20</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" s="79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D20" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="E20" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="F20" s="79" t="s">
-        <v>270</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="M20" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="N20" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O20" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P20" s="41" t="s">
+    <row r="21" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="54">
+        <v>21</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C21" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D21" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F21" s="80" t="s">
         <v>271</v>
       </c>
-      <c r="Q20" s="41" t="s">
+      <c r="G21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M21" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N21" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>API Método</v>
+      </c>
+      <c r="O21" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P21" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="R20" s="41" t="s">
+      <c r="Q21" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="S20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T20" s="41" t="str">
+      <c r="R21" s="39" t="s">
+        <v>274</v>
+      </c>
+      <c r="S21" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="U20" s="41" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U21" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="V20" s="65" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V21" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W20" s="41" t="s">
+        <v>API Método</v>
+      </c>
+      <c r="W21" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X20" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-EGC-20</v>
-      </c>
-      <c r="Y20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="41" t="s">
+      <c r="X21" s="55" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-EGC-21</v>
+      </c>
+      <c r="Y21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="57">
-        <v>21</v>
-      </c>
-      <c r="B21" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="C21" s="79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="E21" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" s="79" t="s">
-        <v>274</v>
-      </c>
-      <c r="G21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="M21" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="N21" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O21" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P21" s="41" t="s">
+    <row r="22" spans="1:30" s="76" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="54">
+        <v>22</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="80" t="s">
+        <v>284</v>
+      </c>
+      <c r="E22" s="80" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="Q21" s="41" t="s">
+      <c r="G22" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M22" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v>API.Macros.Visuais</v>
+      </c>
+      <c r="N22" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>API Método Visual</v>
+      </c>
+      <c r="O22" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P22" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="R21" s="41" t="s">
+      <c r="Q22" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="S21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="41" t="str">
+      <c r="R22" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="S22" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="U21" s="41" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U22" s="39" t="str">
         <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="V21" s="65" t="str">
+        <v>API Macros Visuais</v>
+      </c>
+      <c r="V22" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W21" s="41" t="s">
+        <v>API Método Visual</v>
+      </c>
+      <c r="W22" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="X21" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-EGC-21</v>
-      </c>
-      <c r="Y21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD21" s="41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="57">
-        <v>22</v>
-      </c>
-      <c r="B22" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="C22" s="79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D22" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="E22" s="79" t="s">
-        <v>278</v>
-      </c>
-      <c r="F22" s="79" t="s">
-        <v>279</v>
-      </c>
-      <c r="G22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="M22" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="N22" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O22" s="49" t="str">
-        <f t="shared" si="11"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P22" s="41" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q22" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="R22" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="S22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="41" t="str">
-        <f t="shared" si="12"/>
-        <v>De API</v>
-      </c>
-      <c r="U22" s="41" t="str">
-        <f t="shared" si="12"/>
-        <v>Macros</v>
-      </c>
-      <c r="V22" s="65" t="str">
-        <f t="shared" si="12"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="W22" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="X22" s="58" t="str">
-        <f t="shared" si="3"/>
+      <c r="X22" s="55" t="str">
+        <f t="shared" si="15"/>
         <v>Key-EGC-22</v>
       </c>
-      <c r="Y22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD22" s="41" t="s">
+      <c r="Y22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="62" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B22">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B17 A18:A22">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:F22">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F16">
-    <cfRule type="duplicateValues" dxfId="11" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F21">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18:F22">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -5773,72 +5822,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="Q1" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="33" t="s">
+      <c r="T1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="33" t="s">
+      <c r="U1" s="31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="32">
+      <c r="A2" s="30">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5905,7 +5954,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5926,13 +5975,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29">
-        <v>1</v>
-      </c>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="27">
+        <v>1</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5940,16 +5989,16 @@
       <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5964,36 +6013,36 @@
   <sheetFormatPr defaultColWidth="2.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" customWidth="1"/>
-    <col min="5" max="5" width="3.5703125" style="56" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="53" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.140625" customWidth="1"/>
     <col min="9" max="9" width="47.5703125" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="4" style="56" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4" style="53" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="52" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="52" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.42578125" style="52" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="56" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" style="53" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="3.85546875" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="56" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.42578125" style="56" customWidth="1"/>
-    <col min="30" max="30" width="7.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.28515625" style="56" customWidth="1"/>
+    <col min="27" max="27" width="3.85546875" style="53" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" style="53" customWidth="1"/>
+    <col min="30" max="30" width="7.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.28515625" style="53" customWidth="1"/>
     <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -6007,2401 +6056,2401 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="53" t="s">
+      <c r="M1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="53" t="s">
+      <c r="O1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="P1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="53" t="s">
+      <c r="Q1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="26" t="s">
+      <c r="R1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="53" t="s">
+      <c r="S1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="26" t="s">
+      <c r="T1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="53" t="s">
+      <c r="U1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="V1" s="26" t="s">
+      <c r="V1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="53" t="s">
+      <c r="W1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="X1" s="28" t="s">
+      <c r="X1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Y1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" s="26" t="s">
+      <c r="Z1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="AA1" s="26" t="s">
+      <c r="AA1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="AB1" s="26" t="s">
+      <c r="AB1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" s="26" t="s">
+      <c r="AC1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="AD1" s="26" t="s">
+      <c r="AD1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="AE1" s="26" t="s">
+      <c r="AE1" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="AF1" s="28" t="s">
+      <c r="AF1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AG1" s="39" t="s">
+      <c r="AG1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="28" t="s">
+      <c r="AH1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AI1" s="39" t="s">
+      <c r="AI1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AJ1" s="28" t="s">
+      <c r="AJ1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AK1" s="39" t="s">
+      <c r="AK1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AL1" s="28" t="s">
+      <c r="AL1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AM1" s="39" t="s">
+      <c r="AM1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AN1" s="28" t="s">
+      <c r="AN1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AO1" s="39" t="s">
+      <c r="AO1" s="37" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77">
+      <c r="A2" s="73">
         <v>2</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="35" t="s">
+      <c r="D2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M2" s="54">
+      <c r="M2" s="51">
         <v>1.05</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="O2" s="54">
+      <c r="O2" s="51">
         <v>1.05</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="Q2" s="54">
+      <c r="Q2" s="51">
         <v>0</v>
       </c>
-      <c r="R2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="74" t="s">
+      <c r="R2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77">
+      <c r="A3" s="73">
         <v>3</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="35" t="s">
+      <c r="D3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M3" s="54">
+      <c r="M3" s="51">
         <v>1.05</v>
       </c>
-      <c r="N3" s="36" t="s">
+      <c r="N3" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="O3" s="54">
+      <c r="O3" s="51">
         <v>1.05</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="P3" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="Q3" s="54">
+      <c r="Q3" s="51">
         <v>0</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="S3" s="54">
+      <c r="S3" s="51">
         <v>5.2</v>
       </c>
-      <c r="T3" s="36" t="s">
+      <c r="T3" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="51">
         <v>0</v>
       </c>
-      <c r="V3" s="36" t="s">
+      <c r="V3" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="W3" s="54">
+      <c r="W3" s="51">
         <v>0</v>
       </c>
-      <c r="X3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO3" s="74" t="s">
+      <c r="X3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77">
+      <c r="A4" s="73">
         <v>4</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="35" t="s">
+      <c r="D4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="K4" s="37" t="s">
+      <c r="K4" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M4" s="54">
+      <c r="M4" s="51">
         <v>2.0499999999999998</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="O4" s="54">
+      <c r="O4" s="51">
         <v>2.0499999999999998</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="Q4" s="54">
+      <c r="Q4" s="51">
         <v>0</v>
       </c>
-      <c r="R4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X4" s="36" t="s">
+      <c r="R4" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="35">
         <v>45</v>
       </c>
-      <c r="Z4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO4" s="74" t="s">
+      <c r="Z4" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77">
+      <c r="A5" s="73">
         <v>5</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="35" t="s">
+      <c r="D5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M5" s="54">
+      <c r="M5" s="51">
         <v>3.05</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="O5" s="54">
+      <c r="O5" s="51">
         <v>3.05</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="Q5" s="54">
+      <c r="Q5" s="51">
         <v>0</v>
       </c>
-      <c r="R5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X5" s="36" t="s">
+      <c r="R5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="35">
         <v>1.5</v>
       </c>
-      <c r="Z5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="74" t="s">
+      <c r="Z5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="77">
+      <c r="A6" s="73">
         <v>6</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="35" t="s">
+      <c r="D6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="L6" s="36" t="s">
+      <c r="L6" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="51">
         <v>4.05</v>
       </c>
-      <c r="N6" s="36" t="s">
+      <c r="N6" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="51">
         <v>4.05</v>
       </c>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="51">
         <v>0</v>
       </c>
-      <c r="R6" s="35" t="s">
+      <c r="R6" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="51">
         <v>14.05</v>
       </c>
-      <c r="T6" s="35" t="s">
+      <c r="T6" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="51">
         <v>14.05</v>
       </c>
-      <c r="V6" s="35" t="s">
+      <c r="V6" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="W6" s="54">
+      <c r="W6" s="51">
         <v>0</v>
       </c>
-      <c r="X6" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="74" t="s">
+      <c r="X6" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="77">
+      <c r="A7" s="73">
         <v>7</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="35" t="s">
+      <c r="D7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="J7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="74" t="s">
+      <c r="J7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="77">
+      <c r="A8" s="73">
         <v>8</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="35" t="s">
+      <c r="D8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="J8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO8" s="74" t="s">
+      <c r="J8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="77">
+      <c r="A9" s="73">
         <v>9</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="76" t="s">
+      <c r="G9" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="J9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="74" t="s">
+      <c r="J9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="77">
+      <c r="A10" s="73">
         <v>10</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="76" t="s">
+      <c r="G10" s="72" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="J10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO10" s="74" t="s">
+      <c r="J10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77">
+      <c r="A11" s="73">
         <v>11</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="35" t="s">
+      <c r="D11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="J11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO11" s="74" t="s">
+      <c r="J11" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77">
+      <c r="A12" s="73">
         <v>12</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="35" t="s">
+      <c r="D12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="J12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="36" t="s">
+      <c r="J12" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="Y12" s="37" t="s">
+      <c r="Y12" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="Z12" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="74" t="s">
+      <c r="Z12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="77">
+      <c r="A13" s="73">
         <v>13</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="35" t="s">
+      <c r="D13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="J13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V13" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X13" s="36" t="s">
+      <c r="J13" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="35">
         <v>90</v>
       </c>
-      <c r="Z13" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO13" s="74" t="s">
+      <c r="Z13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="77">
+      <c r="A14" s="73">
         <v>14</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="35" t="s">
+      <c r="D14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="J14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P14" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" s="36" t="s">
+      <c r="J14" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="35">
         <v>60</v>
       </c>
-      <c r="Z14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO14" s="74" t="s">
+      <c r="Z14" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="70" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="77">
+    <row r="15" spans="1:41" s="69" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="73">
         <v>15</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U15" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V15" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X15" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="64" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA15" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB15" s="64" t="s">
         <v>239</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>274</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="J15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="68" t="s">
+      <c r="AC15" s="65" t="s">
         <v>240</v>
       </c>
-      <c r="AA15" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB15" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC15" s="69" t="s">
-        <v>243</v>
-      </c>
-      <c r="AD15" s="71" t="str">
+      <c r="AD15" s="67" t="str">
         <f t="shared" ref="AD15:AD19" si="0">IF(AE15="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="AE15" s="72" t="s">
+      <c r="AE15" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="AF15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="70" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" s="69" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="73">
+        <v>16</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="65" t="s">
         <v>245</v>
       </c>
-      <c r="AF15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO15" s="74" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="77">
-        <v>16</v>
-      </c>
-      <c r="B16" s="67" t="s">
-        <v>246</v>
-      </c>
-      <c r="C16" s="79" t="s">
-        <v>274</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16" s="69" t="s">
-        <v>248</v>
-      </c>
-      <c r="J16" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P16" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA16" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB16" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC16" s="69" t="s">
-        <v>247</v>
-      </c>
-      <c r="AD16" s="71" t="str">
+      <c r="J16" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="64" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA16" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB16" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC16" s="65" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD16" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE16" s="72" t="s">
+      <c r="AE16" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="AF16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="70" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" s="69" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="73">
+        <v>17</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="AF16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="74" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="77">
-        <v>17</v>
-      </c>
-      <c r="B17" s="67" t="s">
-        <v>250</v>
-      </c>
-      <c r="C17" s="79" t="s">
-        <v>274</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="J17" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P17" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R17" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V17" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X17" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA17" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB17" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC17" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD17" s="71" t="str">
+      <c r="J17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="64" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA17" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB17" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC17" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="AD17" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE17" s="72" t="s">
+      <c r="AE17" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="AF17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="70" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:41" s="69" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="73">
+        <v>18</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="65" t="s">
         <v>253</v>
       </c>
-      <c r="AF17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO17" s="74" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="77">
-        <v>18</v>
-      </c>
-      <c r="B18" s="67" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="79" t="s">
-        <v>274</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" s="69" t="s">
-        <v>256</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P18" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X18" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA18" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB18" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC18" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD18" s="71" t="str">
+      <c r="J18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="64" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA18" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB18" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC18" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD18" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE18" s="72" t="s">
+      <c r="AE18" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="70" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:41" s="69" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="73">
+        <v>19</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="65" t="s">
         <v>257</v>
       </c>
-      <c r="AF18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="74" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" s="73" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="77">
-        <v>19</v>
-      </c>
-      <c r="B19" s="67" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" s="79" t="s">
-        <v>274</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="I19" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="J19" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N19" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="P19" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="R19" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="U19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V19" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="W19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X19" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA19" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB19" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC19" s="69" t="s">
-        <v>259</v>
-      </c>
-      <c r="AD19" s="71" t="str">
+      <c r="J19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="U19" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="W19" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="64" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA19" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB19" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC19" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD19" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="AE19" s="72" t="s">
-        <v>261</v>
-      </c>
-      <c r="AF19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO19" s="74" t="s">
+      <c r="AE19" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="AF19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="70" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B2 B3:B14 H1:I14 A3:A19">
-    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B19">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AO19">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Genetica.xlsx
+++ b/Versão5/PRO/Ontologia_Genetica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4B0013-E011-45F0-A671-E7BA1A893432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC6CDC4-6057-4ECC-B8BC-D8F8369BF514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="332">
   <si>
     <t>Key</t>
   </si>
@@ -1427,12 +1427,6 @@
     <t>Autor</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -1452,21 +1446,6 @@
   </si>
   <si>
     <t>Escola Politécnica da UFRJ</t>
-  </si>
-  <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>DataHora</t>
@@ -2120,6 +2099,165 @@
   </si>
   <si>
     <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
@@ -2129,7 +2267,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2302,8 +2440,16 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2466,6 +2612,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2515,10 +2673,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2760,55 +2919,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -2925,6 +3068,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3243,61 +3394,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>62</v>
-      </c>
       <c r="C4" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="14" t="str">
@@ -3305,11 +3456,11 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>54</v>
       </c>
       <c r="B6" s="14" t="str">
@@ -3317,234 +3468,496 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>65</v>
-      </c>
       <c r="C9" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>66</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>279</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>57</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>280</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>58</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>281</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>67</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>282</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>68</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>283</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>69</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>284</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>70</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>285</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>59</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46274.378820370373</v>
+        <v>46276.434053703706</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="32" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="32" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>105</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="B20" s="42" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="32" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>106</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="32" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="B21" s="42" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>104</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" s="84" t="s">
+        <v>309</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B28" s="85" t="s">
+        <v>310</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B29" s="85" t="s">
+        <v>311</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B32" s="87" t="s">
+        <v>314</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B33" s="87" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="88" t="s">
+        <v>316</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B35" s="88" t="s">
+        <v>317</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B36" s="87" t="s">
+        <v>318</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B37" s="88" t="s">
+        <v>319</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B38" s="87" t="s">
+        <v>320</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" s="89" t="s">
+        <v>321</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B40" s="89" t="s">
+        <v>322</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B41" s="90" t="s">
+        <v>323</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B42" s="91" t="s">
+        <v>324</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B43" s="91" t="s">
+        <v>325</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="B44" s="91" t="s">
+        <v>326</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B45" s="91" t="s">
+        <v>327</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B46" s="91" t="s">
+        <v>328</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="B47" s="91" t="s">
+        <v>329</v>
+      </c>
+      <c r="C47" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="B48" s="91" t="s">
+        <v>330</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B49" s="91" t="s">
+        <v>331</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{B0EC9726-36F2-4A4F-AD09-F0A2F86CF49A}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{9F6FF6EC-7353-4B7A-8D4A-1CAEAE3BA080}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{2BAD610A-6CCB-4B92-B34F-1CE42C0493B7}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{0E81DC09-58D1-44E6-BE32-AB6805DB5BB3}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{00CE32DF-67ED-456C-9D95-F24EA07F16B8}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{741BE89D-EFF9-49B0-8043-01E919E092B1}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{48D299E5-44AE-4115-9824-6C7182D4BEA3}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -3586,22 +3999,22 @@
   <sheetData>
     <row r="1" spans="1:30" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>84</v>
-      </c>
       <c r="F1" s="21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G1" s="48" t="s">
         <v>39</v>
@@ -3631,49 +4044,49 @@
         <v>44</v>
       </c>
       <c r="P1" s="22" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="R1" s="38" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="S1" s="81" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="V1" s="23" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="W1" s="22" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="X1" s="56" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AC1" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="AD1" s="22" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3681,19 +4094,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C2" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E2" s="78" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G2" s="49" t="s">
         <v>1</v>
@@ -3727,13 +4140,13 @@
         <v>Valor.X</v>
       </c>
       <c r="P2" s="46" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="Q2" s="46" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="S2" s="75" t="s">
         <v>1</v>
@@ -3751,10 +4164,10 @@
         <v>EGC.Parâmetros</v>
       </c>
       <c r="W2" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X2" s="55" t="str">
-        <f t="shared" ref="X2:X22" si="3">CONCATENATE("Key-EGC-",A2)</f>
+        <f t="shared" ref="X2:X17" si="3">CONCATENATE("Key-EGC-",A2)</f>
         <v>Key-EGC-2</v>
       </c>
       <c r="Y2" s="62" t="s">
@@ -3781,19 +4194,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C3" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E3" s="78" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F3" s="79" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G3" s="49" t="s">
         <v>1</v>
@@ -3827,13 +4240,13 @@
         <v>Valor.Y</v>
       </c>
       <c r="P3" s="46" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="R3" s="39" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="S3" s="75" t="s">
         <v>1</v>
@@ -3851,7 +4264,7 @@
         <v>EGC.Parâmetros</v>
       </c>
       <c r="W3" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X3" s="55" t="str">
         <f t="shared" si="3"/>
@@ -3881,19 +4294,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C4" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E4" s="78" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F4" s="79" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G4" s="49" t="s">
         <v>1</v>
@@ -3927,13 +4340,13 @@
         <v>Valor.Z</v>
       </c>
       <c r="P4" s="46" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="Q4" s="46" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="S4" s="75" t="s">
         <v>1</v>
@@ -3951,7 +4364,7 @@
         <v>EGC.Parâmetros</v>
       </c>
       <c r="W4" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X4" s="55" t="str">
         <f t="shared" si="3"/>
@@ -3981,19 +4394,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C5" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D5" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E5" s="78" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F5" s="79" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>1</v>
@@ -4027,13 +4440,13 @@
         <v>Valor.Distância</v>
       </c>
       <c r="P5" s="46" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="Q5" s="46" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="S5" s="75" t="s">
         <v>1</v>
@@ -4051,7 +4464,7 @@
         <v>EGC.Parâmetros</v>
       </c>
       <c r="W5" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X5" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4081,19 +4494,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C6" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E6" s="78" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F6" s="79" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G6" s="49" t="s">
         <v>1</v>
@@ -4127,13 +4540,13 @@
         <v>Valor.Angular</v>
       </c>
       <c r="P6" s="46" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Q6" s="46" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="R6" s="39" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="S6" s="75" t="s">
         <v>1</v>
@@ -4151,7 +4564,7 @@
         <v>EGC.Parâmetros</v>
       </c>
       <c r="W6" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X6" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4181,19 +4594,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C7" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E7" s="78" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F7" s="79" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>1</v>
@@ -4227,13 +4640,13 @@
         <v>Valor.Escalar</v>
       </c>
       <c r="P7" s="46" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="Q7" s="46" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="S7" s="75" t="s">
         <v>1</v>
@@ -4251,7 +4664,7 @@
         <v>EGC.Parâmetros</v>
       </c>
       <c r="W7" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X7" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4281,19 +4694,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C8" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E8" s="78" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F8" s="79" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G8" s="49" t="s">
         <v>1</v>
@@ -4327,13 +4740,13 @@
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P8" s="46" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="Q8" s="46" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="R8" s="39" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="S8" s="75" t="s">
         <v>1</v>
@@ -4351,7 +4764,7 @@
         <v>EGC.Bases</v>
       </c>
       <c r="W8" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X8" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4381,19 +4794,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C9" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D9" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E9" s="78" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F9" s="79" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>1</v>
@@ -4427,13 +4840,13 @@
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P9" s="46" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="Q9" s="46" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="R9" s="39" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="S9" s="75" t="s">
         <v>1</v>
@@ -4451,7 +4864,7 @@
         <v>EGC.Bases</v>
       </c>
       <c r="W9" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X9" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4481,19 +4894,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C10" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E10" s="78" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F10" s="79" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G10" s="49" t="s">
         <v>1</v>
@@ -4527,13 +4940,13 @@
         <v>Ponto.Base</v>
       </c>
       <c r="P10" s="46" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q10" s="46" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="R10" s="39" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="S10" s="75" t="s">
         <v>1</v>
@@ -4551,7 +4964,7 @@
         <v>EGC.Bases</v>
       </c>
       <c r="W10" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X10" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4581,19 +4994,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C11" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D11" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E11" s="78" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F11" s="79" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>1</v>
@@ -4627,13 +5040,13 @@
         <v>Ponto.Destino</v>
       </c>
       <c r="P11" s="46" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="Q11" s="46" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="R11" s="39" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="S11" s="75" t="s">
         <v>1</v>
@@ -4651,7 +5064,7 @@
         <v>EGC.Bases</v>
       </c>
       <c r="W11" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X11" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4681,19 +5094,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C12" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E12" s="78" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F12" s="79" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G12" s="49" t="s">
         <v>1</v>
@@ -4708,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="49" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="L12" s="46" t="str">
         <f t="shared" ref="L12" si="4">_xlfn.CONCAT(C12)</f>
@@ -4727,13 +5140,13 @@
         <v>Translação.XYZ</v>
       </c>
       <c r="P12" s="46" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Q12" s="46" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="R12" s="39" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="S12" s="75" t="s">
         <v>1</v>
@@ -4751,7 +5164,7 @@
         <v>EGC.Movimentos</v>
       </c>
       <c r="W12" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X12" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4781,19 +5194,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C13" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D13" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E13" s="78" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F13" s="79" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G13" s="49" t="s">
         <v>1</v>
@@ -4808,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="49" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="L13" s="46" t="str">
         <f t="shared" si="0"/>
@@ -4827,13 +5240,13 @@
         <v>Translação.Polar</v>
       </c>
       <c r="P13" s="46" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="Q13" s="46" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="R13" s="39" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="S13" s="75" t="s">
         <v>1</v>
@@ -4851,7 +5264,7 @@
         <v>EGC.Movimentos</v>
       </c>
       <c r="W13" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X13" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4881,19 +5294,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C14" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D14" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E14" s="78" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F14" s="79" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G14" s="49" t="s">
         <v>1</v>
@@ -4908,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="49" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="L14" s="46" t="str">
         <f t="shared" si="0"/>
@@ -4927,13 +5340,13 @@
         <v>Giro</v>
       </c>
       <c r="P14" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="Q14" s="46" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R14" s="39" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="S14" s="75" t="s">
         <v>1</v>
@@ -4951,7 +5364,7 @@
         <v>EGC.Movimentos</v>
       </c>
       <c r="W14" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X14" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4981,19 +5394,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C15" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D15" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E15" s="78" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F15" s="79" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>1</v>
@@ -5008,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="49" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="L15" s="46" t="str">
         <f t="shared" si="0"/>
@@ -5027,13 +5440,13 @@
         <v>Escalar</v>
       </c>
       <c r="P15" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="Q15" s="46" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="R15" s="39" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="S15" s="75" t="s">
         <v>1</v>
@@ -5051,7 +5464,7 @@
         <v>EGC.Movimentos</v>
       </c>
       <c r="W15" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X15" s="55" t="str">
         <f t="shared" si="3"/>
@@ -5081,19 +5494,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C16" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="78" t="s">
-        <v>220</v>
-      </c>
       <c r="E16" s="78" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F16" s="79" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G16" s="49" t="s">
         <v>1</v>
@@ -5108,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="49" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="L16" s="46" t="str">
         <f t="shared" si="0"/>
@@ -5127,13 +5540,13 @@
         <v>Reflexão</v>
       </c>
       <c r="P16" s="46" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="Q16" s="46" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="R16" s="39" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="S16" s="75" t="s">
         <v>1</v>
@@ -5151,7 +5564,7 @@
         <v>EGC.Movimentos</v>
       </c>
       <c r="W16" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X16" s="55" t="str">
         <f t="shared" si="3"/>
@@ -5181,19 +5594,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D17" s="80" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>1</v>
@@ -5211,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="47" t="str">
-        <f t="shared" ref="L17:O22" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
+        <f t="shared" ref="L17:O17" si="11">SUBSTITUTE(CONCATENATE("", C17), ".", " ")</f>
         <v>Morfológico</v>
       </c>
       <c r="M17" s="47" t="str">
@@ -5227,13 +5640,13 @@
         <v>Código De Forma</v>
       </c>
       <c r="P17" s="39" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Q17" s="59" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="R17" s="39" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="S17" s="75" t="s">
         <v>1</v>
@@ -5251,7 +5664,7 @@
         <v>Códificação Formal</v>
       </c>
       <c r="W17" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X17" s="55" t="str">
         <f t="shared" si="3"/>
@@ -5281,19 +5694,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D18" s="80" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E18" s="80" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>1</v>
@@ -5327,13 +5740,13 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P18" s="39" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Q18" s="39" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="R18" s="39" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="S18" s="75" t="s">
         <v>1</v>
@@ -5351,7 +5764,7 @@
         <v>API Método</v>
       </c>
       <c r="W18" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X18" s="55" t="str">
         <f t="shared" ref="X18:X22" si="15">CONCATENATE("Key-EGC-",A18)</f>
@@ -5381,19 +5794,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D19" s="80" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E19" s="80" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G19" s="58" t="s">
         <v>1</v>
@@ -5427,13 +5840,13 @@
         <v>Função Global</v>
       </c>
       <c r="P19" s="39" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="Q19" s="39" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="R19" s="39" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="S19" s="75" t="s">
         <v>1</v>
@@ -5451,7 +5864,7 @@
         <v>API Método</v>
       </c>
       <c r="W19" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X19" s="55" t="str">
         <f t="shared" si="15"/>
@@ -5481,19 +5894,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D20" s="80" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E20" s="80" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F20" s="80" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>1</v>
@@ -5527,13 +5940,13 @@
         <v>Função Local</v>
       </c>
       <c r="P20" s="39" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="Q20" s="39" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="R20" s="39" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="S20" s="75" t="s">
         <v>1</v>
@@ -5551,7 +5964,7 @@
         <v>API Método</v>
       </c>
       <c r="W20" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X20" s="55" t="str">
         <f t="shared" si="15"/>
@@ -5581,19 +5994,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D21" s="80" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E21" s="80" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G21" s="58" t="s">
         <v>1</v>
@@ -5627,13 +6040,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P21" s="39" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="Q21" s="39" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="R21" s="39" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="S21" s="75" t="s">
         <v>1</v>
@@ -5651,7 +6064,7 @@
         <v>API Método</v>
       </c>
       <c r="W21" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X21" s="55" t="str">
         <f t="shared" si="15"/>
@@ -5681,19 +6094,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="57" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C22" s="80" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D22" s="80" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E22" s="80" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F22" s="80" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="G22" s="58" t="s">
         <v>1</v>
@@ -5727,13 +6140,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P22" s="39" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="Q22" s="39" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="R22" s="39" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="S22" s="75" t="s">
         <v>1</v>
@@ -5751,7 +6164,7 @@
         <v>API Método Visual</v>
       </c>
       <c r="W22" s="39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="X22" s="55" t="str">
         <f t="shared" si="15"/>
@@ -5778,29 +6191,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B17 A18:A22">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F16">
-    <cfRule type="duplicateValues" dxfId="16" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18:F22">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17">
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F22">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -5954,7 +6367,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5979,10 +6392,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5998,7 +6411,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6057,7 +6470,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>49</v>
@@ -6069,115 +6482,115 @@
         <v>48</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="O1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="R1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="S1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="T1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="U1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="V1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="W1" s="50" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="X1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="Y1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="Z1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="AA1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AB1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="AC1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AD1" s="24" t="s">
         <v>48</v>
       </c>
       <c r="AE1" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AF1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="AG1" s="37" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AH1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="AI1" s="37" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AJ1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="AK1" s="37" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AL1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="AM1" s="37" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AN1" s="26" t="s">
         <v>48</v>
       </c>
       <c r="AO1" s="37" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -6185,10 +6598,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>1</v>
@@ -6203,31 +6616,31 @@
         <v>1</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M2" s="51">
         <v>1.05</v>
       </c>
       <c r="N2" s="34" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O2" s="51">
         <v>1.05</v>
       </c>
       <c r="P2" s="34" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q2" s="51">
         <v>0</v>
@@ -6310,10 +6723,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>1</v>
@@ -6328,49 +6741,49 @@
         <v>1</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I3" s="35" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M3" s="51">
         <v>1.05</v>
       </c>
       <c r="N3" s="34" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O3" s="51">
         <v>1.05</v>
       </c>
       <c r="P3" s="34" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q3" s="51">
         <v>0</v>
       </c>
       <c r="R3" s="34" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="S3" s="51">
         <v>5.2</v>
       </c>
       <c r="T3" s="34" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="U3" s="51">
         <v>0</v>
       </c>
       <c r="V3" s="34" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="W3" s="51">
         <v>0</v>
@@ -6435,49 +6848,49 @@
         <v>4</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>120</v>
-      </c>
       <c r="L4" s="34" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M4" s="51">
         <v>2.0499999999999998</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O4" s="51">
         <v>2.0499999999999998</v>
       </c>
       <c r="P4" s="34" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q4" s="51">
         <v>0</v>
@@ -6501,7 +6914,7 @@
         <v>1</v>
       </c>
       <c r="X4" s="34" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Y4" s="35">
         <v>45</v>
@@ -6560,49 +6973,49 @@
         <v>5</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C5" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>121</v>
-      </c>
       <c r="L5" s="34" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M5" s="51">
         <v>3.05</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O5" s="51">
         <v>3.05</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q5" s="51">
         <v>0</v>
@@ -6626,7 +7039,7 @@
         <v>1</v>
       </c>
       <c r="X5" s="34" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y5" s="35">
         <v>1.5</v>
@@ -6685,67 +7098,67 @@
         <v>6</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C6" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="K6" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>122</v>
-      </c>
       <c r="L6" s="34" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M6" s="51">
         <v>4.05</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O6" s="51">
         <v>4.05</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q6" s="51">
         <v>0</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="S6" s="51">
         <v>14.05</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="U6" s="51">
         <v>14.05</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="W6" s="51">
         <v>0</v>
@@ -6810,10 +7223,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D7" s="45" t="s">
         <v>1</v>
@@ -6828,10 +7241,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I7" s="35" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="J7" s="34" t="s">
         <v>1</v>
@@ -6935,10 +7348,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>1</v>
@@ -6953,10 +7366,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="J8" s="34" t="s">
         <v>1</v>
@@ -7060,28 +7473,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E9" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="44" t="s">
-        <v>137</v>
-      </c>
       <c r="G9" s="72" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J9" s="34" t="s">
         <v>1</v>
@@ -7185,28 +7598,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E10" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="F10" s="44" t="s">
-        <v>137</v>
-      </c>
       <c r="G10" s="72" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I10" s="35" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J10" s="34" t="s">
         <v>1</v>
@@ -7310,10 +7723,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D11" s="45" t="s">
         <v>1</v>
@@ -7328,10 +7741,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="J11" s="34" t="s">
         <v>1</v>
@@ -7435,10 +7848,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D12" s="45" t="s">
         <v>1</v>
@@ -7453,10 +7866,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="J12" s="34" t="s">
         <v>1</v>
@@ -7501,10 +7914,10 @@
         <v>1</v>
       </c>
       <c r="X12" s="34" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Y12" s="35" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Z12" s="33" t="s">
         <v>1</v>
@@ -7560,10 +7973,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D13" s="45" t="s">
         <v>1</v>
@@ -7578,10 +7991,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I13" s="35" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J13" s="34" t="s">
         <v>1</v>
@@ -7626,7 +8039,7 @@
         <v>1</v>
       </c>
       <c r="X13" s="34" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Y13" s="35">
         <v>90</v>
@@ -7685,10 +8098,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D14" s="45" t="s">
         <v>1</v>
@@ -7703,10 +8116,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J14" s="34" t="s">
         <v>1</v>
@@ -7751,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="34" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Y14" s="35">
         <v>60</v>
@@ -7810,10 +8223,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C15" s="74" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D15" s="45" t="s">
         <v>1</v>
@@ -7828,10 +8241,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I15" s="65" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J15" s="34" t="s">
         <v>1</v>
@@ -7882,23 +8295,23 @@
         <v>1</v>
       </c>
       <c r="Z15" s="64" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AA15" s="65" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AB15" s="64" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AC15" s="65" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AD15" s="67" t="str">
         <f t="shared" ref="AD15:AD19" si="0">IF(AE15="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="AE15" s="68" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AF15" s="45" t="s">
         <v>1</v>
@@ -7936,10 +8349,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C16" s="74" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D16" s="45" t="s">
         <v>1</v>
@@ -7954,10 +8367,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I16" s="65" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J16" s="34" t="s">
         <v>1</v>
@@ -8008,23 +8421,23 @@
         <v>1</v>
       </c>
       <c r="Z16" s="64" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA16" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB16" s="64" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC16" s="65" t="s">
         <v>237</v>
-      </c>
-      <c r="AA16" s="65" t="s">
-        <v>238</v>
-      </c>
-      <c r="AB16" s="64" t="s">
-        <v>239</v>
-      </c>
-      <c r="AC16" s="65" t="s">
-        <v>244</v>
       </c>
       <c r="AD16" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="AE16" s="68" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AF16" s="45" t="s">
         <v>1</v>
@@ -8062,10 +8475,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C17" s="74" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D17" s="45" t="s">
         <v>1</v>
@@ -8080,10 +8493,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I17" s="65" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J17" s="34" t="s">
         <v>1</v>
@@ -8134,23 +8547,23 @@
         <v>1</v>
       </c>
       <c r="Z17" s="64" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AA17" s="65" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AB17" s="64" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AC17" s="65" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AD17" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="AE17" s="68" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AF17" s="45" t="s">
         <v>1</v>
@@ -8188,10 +8601,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C18" s="74" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D18" s="45" t="s">
         <v>1</v>
@@ -8206,10 +8619,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I18" s="65" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="J18" s="34" t="s">
         <v>1</v>
@@ -8260,23 +8673,23 @@
         <v>1</v>
       </c>
       <c r="Z18" s="64" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AA18" s="65" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AB18" s="64" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AC18" s="65" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AD18" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="AE18" s="68" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AF18" s="45" t="s">
         <v>1</v>
@@ -8314,10 +8727,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C19" s="74" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D19" s="45" t="s">
         <v>1</v>
@@ -8332,10 +8745,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I19" s="65" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J19" s="34" t="s">
         <v>1</v>
@@ -8386,23 +8799,23 @@
         <v>1</v>
       </c>
       <c r="Z19" s="64" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AA19" s="65" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AB19" s="64" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AC19" s="65" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AD19" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="AE19" s="68" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AF19" s="45" t="s">
         <v>1</v>
@@ -8438,19 +8851,19 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B2 B3:B14 H1:I14 A3:A19">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B19">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AO19">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
